--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G3" t="n">
         <v>2.08</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
         <v>1.89</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>5.6</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 01:34:35</t>
+          <t>2026-03-29 03:42:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -772,7 +772,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
         <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
         <v>1.86</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 03:42:42</t>
+          <t>2026-03-29 05:51:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
         <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G4" t="n">
         <v>1.88</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 05:51:01</t>
+          <t>2026-03-29 07:59:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -772,7 +772,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 07:59:40</t>
+          <t>2026-03-29 10:07:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G4" t="n">
         <v>1.88</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 10:07:53</t>
+          <t>2026-03-29 12:15:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -748,50 +748,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2.96</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.02</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,201 +1308,395 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 12:15:15</t>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cadiz</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-03-29 14:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Sportivo Luqueno</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>1.01</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-29 12:15:15</t>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-29 14:21:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,16 +775,16 @@
         <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="P2" t="n">
         <v>1.46</v>
@@ -793,134 +793,134 @@
         <v>2.96</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>2.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
@@ -969,152 +969,152 @@
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>3.35</v>
       </c>
       <c r="O3" t="n">
         <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
         <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>15</v>
       </c>
-      <c r="AE3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>3.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>3.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.44</v>
+        <v>3.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.44</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
@@ -1145,177 +1145,177 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.14</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.18</v>
-      </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
         <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,378 +1325,960 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>2.58</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>2.96</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 14:21:59</t>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Southend</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Yeovil</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>English National League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cadiz</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:28:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sportivo Luqueno</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q9" t="n">
         <v>1.01</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-29 14:21:59</t>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:28:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH9"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -775,16 +775,16 @@
         <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="P2" t="n">
         <v>1.46</v>
@@ -793,134 +793,134 @@
         <v>2.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
         <v>1.94</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.84</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>23</v>
-      </c>
       <c r="BA2" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="J3" t="n">
         <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W3" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
         <v>55</v>
       </c>
       <c r="AK3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN3" t="n">
         <v>36</v>
       </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>42</v>
-      </c>
       <c r="AO3" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.55</v>
+        <v>30</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.6</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.65</v>
+        <v>46</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.55</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.6</v>
+        <v>28</v>
       </c>
       <c r="BG3" t="n">
         <v>19.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="H4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I4" t="n">
         <v>3.7</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1172,143 +1172,143 @@
         <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
         <v>15</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI4" t="n">
         <v>50</v>
       </c>
-      <c r="AF4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
         <v>2.38</v>
       </c>
       <c r="G5" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
         <v>2.1</v>
@@ -1375,55 +1375,55 @@
         <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA5" t="n">
         <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG5" t="n">
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>46</v>
@@ -1444,7 +1444,7 @@
         <v>19.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
         <v>13.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G6" t="n">
         <v>1.43</v>
@@ -1542,7 +1542,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
@@ -1557,10 +1557,10 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
         <v>2.26</v>
@@ -1569,16 +1569,16 @@
         <v>1.63</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
         <v>1.08</v>
@@ -1587,101 +1587,101 @@
         <v>3.3</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC6" t="n">
         <v>13</v>
       </c>
-      <c r="AC6" t="n">
-        <v>18</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD6" t="n">
         <v>1.03</v>
       </c>
@@ -1689,14 +1689,14 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.02</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H7" t="n">
         <v>3.65</v>
@@ -1748,13 +1748,13 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
         <v>2.04</v>
@@ -1763,16 +1763,16 @@
         <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
         <v>1.3</v>
@@ -1781,116 +1781,116 @@
         <v>1.9</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF7" t="n">
         <v>15</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AG7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15</v>
-      </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AK7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>30</v>
       </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
@@ -1921,34 +1921,34 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
         <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
         <v>1.81</v>
@@ -1957,328 +1957,522 @@
         <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 16:28:16</t>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Albion FC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-03-29 18:33:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Sportivo Luqueno</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>1.01</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-03-29 16:28:16</t>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-29 18:33:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -778,19 +778,19 @@
         <v>1.66</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="P2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="R2" t="n">
         <v>1.15</v>
@@ -799,22 +799,22 @@
         <v>6.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
@@ -835,92 +835,92 @@
         <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG2" t="n">
         <v>23</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AK2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL2" t="n">
         <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AN2" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
         <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BB2" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="G3" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.55</v>
@@ -981,7 +981,7 @@
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
         <v>2.02</v>
@@ -990,7 +990,7 @@
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.77</v>
@@ -999,55 +999,55 @@
         <v>2.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X3" t="n">
         <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
         <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>100</v>
@@ -1056,46 +1056,46 @@
         <v>36</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>15.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>29</v>
@@ -1104,17 +1104,17 @@
         <v>10.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BG3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.32</v>
@@ -1169,13 +1169,13 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
         <v>1.84</v>
@@ -1184,28 +1184,28 @@
         <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
         <v>70</v>
@@ -1214,101 +1214,101 @@
         <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>38</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
         <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="AT4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY4" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>26</v>
@@ -1405,25 +1405,25 @@
         <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>34</v>
       </c>
       <c r="AF5" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
         <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>46</v>
@@ -1432,7 +1432,7 @@
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>40</v>
@@ -1444,7 +1444,7 @@
         <v>19.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
         <v>13.5</v>
@@ -1453,10 +1453,10 @@
         <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>9.6</v>
@@ -1468,7 +1468,7 @@
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX5" t="n">
         <v>13</v>
@@ -1480,29 +1480,29 @@
         <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1644,13 +1644,13 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>7.8</v>
@@ -1659,10 +1659,10 @@
         <v>10.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7.4</v>
@@ -1671,10 +1671,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
         <v>9.6</v>
@@ -1683,20 +1683,20 @@
         <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>140</v>
+        <v>6.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1781,10 +1781,10 @@
         <v>1.9</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>32</v>
@@ -1793,25 +1793,25 @@
         <v>85</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI7" t="n">
         <v>55</v>
@@ -1829,7 +1829,7 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
         <v>48</v>
@@ -1838,59 +1838,59 @@
         <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
         <v>10.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,7 +1945,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.37</v>
@@ -1954,7 +1954,7 @@
         <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
         <v>1.31</v>
@@ -1969,19 +1969,19 @@
         <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
         <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA8" t="n">
         <v>170</v>
@@ -1993,10 +1993,10 @@
         <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
@@ -2008,7 +2008,7 @@
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
         <v>20</v>
@@ -2035,22 +2035,22 @@
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
         <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>9.199999999999999</v>
@@ -2062,7 +2062,7 @@
         <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>17</v>
@@ -2071,27 +2071,27 @@
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,378 +2101,766 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
         <v>4.4</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.02</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN9" t="n">
         <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>36</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>21</v>
       </c>
-      <c r="BC9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BG9" t="n">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 18:33:26</t>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cuiaba</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-03-29 20:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Albion FC</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-29 20:38:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Sportivo Luqueno</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q12" t="n">
         <v>1.01</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-03-29 18:33:26</t>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-29 20:38:24</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -781,7 +781,7 @@
         <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
         <v>1.63</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>2.62</v>
       </c>
       <c r="I3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -1005,7 +1005,7 @@
         <v>1.48</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
         <v>11.5</v>
@@ -1053,7 +1053,7 @@
         <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
         <v>27</v>
@@ -1062,10 +1062,10 @@
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
         <v>34</v>
@@ -1077,34 +1077,34 @@
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>29</v>
       </c>
       <c r="BD3" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
         <v>21</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1268,7 +1268,7 @@
         <v>9.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
         <v>14</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE6" t="n">
         <v>190</v>
@@ -1644,13 +1644,13 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
         <v>6.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>7.8</v>
@@ -1662,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>7.4</v>
@@ -1671,10 +1671,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB6" t="n">
         <v>9.6</v>
@@ -1683,10 +1683,10 @@
         <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
         <v>4.8</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="G8" t="n">
         <v>1.83</v>
@@ -2032,7 +2032,7 @@
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
         <v>8.4</v>
@@ -2047,7 +2047,7 @@
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
         <v>9.199999999999999</v>
@@ -2080,11 +2080,11 @@
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H10" t="n">
         <v>6</v>
@@ -2324,7 +2324,7 @@
         <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,7 +2333,7 @@
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.45</v>
@@ -2351,22 +2351,22 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
         <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
         <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
         <v>55</v>
@@ -2399,7 +2399,7 @@
         <v>150</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AK10" t="n">
         <v>23</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>
@@ -2715,152 +2715,152 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
         <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-29 20:38:24</t>
+          <t>2026-03-29 22:42:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>730</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>760</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>790</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4.7</v>
       </c>
-      <c r="G2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>370</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>230</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BE2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG2" t="n">
         <v>8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,82 +942,82 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.76</v>
+        <v>2.12</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>2.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="W3" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
         <v>7.8</v>
@@ -1026,49 +1026,49 @@
         <v>12.5</v>
       </c>
       <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="n">
         <v>30</v>
       </c>
-      <c r="AF3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI3" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="AN3" t="n">
+        <v>230</v>
+      </c>
+      <c r="AO3" t="n">
         <v>32</v>
       </c>
-      <c r="AO3" t="n">
-        <v>27</v>
-      </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1077,44 +1077,44 @@
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16</v>
+        <v>7.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF3" t="n">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.86</v>
       </c>
       <c r="G4" t="n">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
         <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>16</v>
       </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="BA4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD4" t="n">
         <v>14</v>
       </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="BE4" t="n">
         <v>14</v>
       </c>
-      <c r="AR4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>11</v>
-      </c>
       <c r="BF4" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR5" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AS5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>34</v>
       </c>
-      <c r="AF5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="G6" t="n">
-        <v>1.43</v>
+        <v>2.48</v>
       </c>
       <c r="H6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I6" t="n">
-        <v>13</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="AZ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>430</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG6" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>430</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>15.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>48</v>
+        <v>250</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.76</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.1</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP8" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="X9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF9" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BE9" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF9" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
@@ -2295,39 +2295,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2336,150 +2336,150 @@
         <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
         <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
         <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>14</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA10" t="n">
         <v>8</v>
       </c>
-      <c r="AS10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
+      <c r="BB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC10" t="n">
         <v>6.8</v>
       </c>
-      <c r="AW10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG10" t="n">
         <v>8</v>
       </c>
-      <c r="BE10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>9</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,373 +2494,761 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>1.78</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
         <v>4.4</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X11" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="AB11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
         <v>8</v>
       </c>
-      <c r="AC11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AS11" t="n">
         <v>9</v>
       </c>
-      <c r="AR11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AT11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB11" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BC11" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-29 22:42:50</t>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Albion FC</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-30 00:48:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Sportivo Luqueno</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.25</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O13" t="n">
         <v>1.37</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P13" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q13" t="n">
         <v>1.37</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>1.18</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S13" t="n">
         <v>1.37</v>
       </c>
-      <c r="T12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-03-29 22:42:50</t>
+      <c r="T13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-30 00:48:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-30 00:48:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I3" t="n">
         <v>2.12</v>
@@ -984,31 +984,31 @@
         <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
         <v>6.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V3" t="n">
         <v>1.89</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="n">
         <v>10.5</v>
@@ -1017,10 +1017,10 @@
         <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1029,31 +1029,31 @@
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH3" t="n">
         <v>30</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ3" t="n">
         <v>180</v>
       </c>
       <c r="AK3" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
         <v>370</v>
       </c>
       <c r="AN3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AO3" t="n">
         <v>32</v>
@@ -1062,13 +1062,13 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
         <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1080,41 +1080,41 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BG3" t="n">
         <v>18.5</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
@@ -1169,37 +1169,37 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
@@ -1220,10 +1220,10 @@
         <v>12.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1256,7 +1256,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR4" t="n">
         <v>15.5</v>
@@ -1280,16 +1280,16 @@
         <v>17</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC4" t="n">
         <v>29</v>
@@ -1298,17 +1298,17 @@
         <v>14</v>
       </c>
       <c r="BE4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
         <v>2.16</v>
@@ -1357,7 +1357,7 @@
         <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1381,7 +1381,7 @@
         <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
         <v>2.18</v>
@@ -1390,7 +1390,7 @@
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
         <v>15.5</v>
@@ -1408,7 +1408,7 @@
         <v>10</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1417,13 +1417,13 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>16</v>
       </c>
       <c r="BA5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE5" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>12.5</v>
       </c>
       <c r="BF5" t="n">
         <v>12.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I7" t="n">
         <v>13</v>
@@ -1742,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1772,7 +1772,7 @@
         <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
         <v>1.08</v>
@@ -1784,13 +1784,13 @@
         <v>27</v>
       </c>
       <c r="Y7" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA7" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AB7" t="n">
         <v>9.6</v>
@@ -1799,10 +1799,10 @@
         <v>13</v>
       </c>
       <c r="AD7" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1811,7 +1811,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>150</v>
@@ -1826,13 +1826,13 @@
         <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN7" t="n">
         <v>6.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
@@ -1841,7 +1841,7 @@
         <v>6</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
         <v>7</v>
@@ -1853,10 +1853,10 @@
         <v>10.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
@@ -1865,7 +1865,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BA7" t="n">
         <v>6.8</v>
@@ -1886,11 +1886,11 @@
         <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1930,19 +1930,19 @@
         <v>3.65</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
         <v>4.2</v>
@@ -1951,25 +1951,25 @@
         <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
         <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
         <v>1.9</v>
@@ -1984,7 +1984,7 @@
         <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
         <v>970</v>
@@ -2026,65 +2026,65 @@
         <v>970</v>
       </c>
       <c r="AO8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP8" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX8" t="n">
         <v>5.4</v>
       </c>
-      <c r="AW8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AY8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD8" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G9" t="n">
         <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>3.65</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2145,7 +2145,7 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
         <v>2.1</v>
@@ -2163,13 +2163,13 @@
         <v>1.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
         <v>2.2</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y9" t="n">
         <v>18.5</v>
@@ -2229,10 +2229,10 @@
         <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9" t="n">
         <v>6.8</v>
@@ -2244,7 +2244,7 @@
         <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX9" t="n">
         <v>9.199999999999999</v>
@@ -2256,7 +2256,7 @@
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB9" t="n">
         <v>17</v>
@@ -2265,20 +2265,20 @@
         <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2426,7 +2426,7 @@
         <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="AT10" t="n">
         <v>6.6</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
         <v>140</v>
@@ -2587,7 +2587,7 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>150</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3106,13 +3106,13 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>1.72</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P14" t="n">
         <v>1.72</v>
@@ -3127,10 +3127,10 @@
         <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
         <v>1.18</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD2" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>730</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>760</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>990</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG2" t="n">
-        <v>790</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
-        <v>990</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE2" t="n">
         <v>55</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF2" t="n">
-        <v>4.8</v>
+        <v>44</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,179 +942,179 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.94</v>
+        <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>6.6</v>
+        <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
       </c>
       <c r="AE3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK3" t="n">
         <v>34</v>
       </c>
-      <c r="AF3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>220</v>
+        <v>36</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BB3" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>95</v>
+        <v>12.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="H4" t="n">
-        <v>2.64</v>
+        <v>3.85</v>
       </c>
       <c r="I4" t="n">
-        <v>2.76</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="X4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX4" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>17</v>
-      </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>970</v>
       </c>
-      <c r="Z5" t="n">
-        <v>29</v>
-      </c>
       <c r="AA5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM5" t="n">
         <v>70</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AN5" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV5" t="n">
         <v>10</v>
       </c>
-      <c r="AC5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14</v>
-      </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>5.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>34</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="G6" t="n">
-        <v>2.48</v>
+        <v>1.43</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AJ6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL6" t="n">
         <v>38</v>
       </c>
-      <c r="AK6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>40</v>
-      </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
-        <v>19.5</v>
+        <v>6.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB6" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC6" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="H7" t="n">
-        <v>9.4</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U7" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="X7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>27</v>
       </c>
-      <c r="Y7" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>400</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>12</v>
-      </c>
       <c r="AK7" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.8</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AW7" t="n">
         <v>7</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BA7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD7" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
         <v>7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.65</v>
       </c>
-      <c r="I8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AK8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
         <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF9" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AG9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW9" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK9" t="n">
+      <c r="BF9" t="n">
         <v>21</v>
       </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="BG9" t="n">
         <v>8</v>
       </c>
-      <c r="AS9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>9</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2336,150 +2336,150 @@
         <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P10" t="n">
         <v>1.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK10" t="n">
         <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
       </c>
       <c r="AL10" t="n">
         <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS10" t="n">
         <v>9</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="AT10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AW10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC10" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BD10" t="n">
         <v>8</v>
       </c>
-      <c r="BB10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>4.4</v>
+        <v>1.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
         <v>970</v>
       </c>
-      <c r="Z11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AJ11" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>17</v>
       </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>7</v>
-      </c>
       <c r="BA11" t="n">
-        <v>8.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>3.45</v>
       </c>
       <c r="BG11" t="n">
-        <v>9</v>
+        <v>3.55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,66 +2683,66 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>1.24</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
         <v>1.02</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -2751,116 +2751,116 @@
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
         <v>1.82</v>
@@ -3133,7 +3133,7 @@
         <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>2.22</v>
@@ -3157,7 +3157,7 @@
         <v>10</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -3169,7 +3169,7 @@
         <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3202,7 +3202,7 @@
         <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AT14" t="n">
         <v>3.85</v>
@@ -3238,7 +3238,7 @@
         <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BF14" t="n">
         <v>10.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,58 +760,58 @@
         <v>4.7</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N2" t="n">
         <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P2" t="n">
         <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S2" t="n">
         <v>6.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W2" t="n">
         <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y2" t="n">
         <v>6</v>
@@ -823,19 +823,19 @@
         <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC2" t="n">
         <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AG2" t="n">
         <v>22</v>
@@ -844,7 +844,7 @@
         <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
         <v>180</v>
@@ -853,13 +853,13 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AN2" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AO2" t="n">
         <v>46</v>
@@ -868,10 +868,10 @@
         <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2" t="n">
         <v>17</v>
@@ -880,19 +880,19 @@
         <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>21</v>
@@ -910,7 +910,7 @@
         <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BF2" t="n">
         <v>44</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G3" t="n">
         <v>3</v>
@@ -960,7 +960,7 @@
         <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -975,31 +975,31 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
         <v>2.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3.65</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
         <v>1.5</v>
@@ -1008,7 +1008,7 @@
         <v>13.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
         <v>18</v>
@@ -1029,7 +1029,7 @@
         <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1038,7 +1038,7 @@
         <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
         <v>50</v>
@@ -1047,28 +1047,28 @@
         <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
         <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AX3" t="n">
         <v>17</v>
@@ -1092,29 +1092,29 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BE3" t="n">
         <v>12.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BG3" t="n">
         <v>22</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>2.06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
         <v>4.1</v>
@@ -1163,10 +1163,10 @@
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
         <v>3.95</v>
@@ -1175,49 +1175,49 @@
         <v>1.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
         <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
         <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
         <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
         <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
@@ -1229,7 +1229,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
@@ -1244,7 +1244,7 @@
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
         <v>15</v>
@@ -1253,25 +1253,25 @@
         <v>55</v>
       </c>
       <c r="AP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
       <c r="AR4" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
         <v>12.5</v>
@@ -1286,19 +1286,19 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB4" t="n">
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
         <v>13</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1339,40 +1339,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1384,55 +1384,55 @@
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
         <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
         <v>15</v>
       </c>
       <c r="AI5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1444,65 +1444,65 @@
         <v>970</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
         <v>4.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="AT5" t="n">
         <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>18.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB5" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BC5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE5" t="n">
         <v>5.3</v>
       </c>
-      <c r="BD5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF5" t="n">
-        <v>19</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
         <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G6" t="n">
         <v>1.43</v>
@@ -1542,10 +1542,10 @@
         <v>9.4</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -1572,16 +1572,16 @@
         <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
         <v>1.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
         <v>3.3</v>
@@ -1593,22 +1593,22 @@
         <v>36</v>
       </c>
       <c r="Z6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA6" t="n">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="AB6" t="n">
         <v>9.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AE6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
@@ -1617,86 +1617,86 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
         <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO6" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX6" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AY6" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AZ6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AV6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G7" t="n">
         <v>2.16</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
@@ -1745,7 +1745,7 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -1754,52 +1754,52 @@
         <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.9</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
         <v>46</v>
@@ -1814,83 +1814,83 @@
         <v>970</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN7" t="n">
         <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AR7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
         <v>6.6</v>
       </c>
-      <c r="AS7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7</v>
-      </c>
       <c r="AX7" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BB7" t="n">
         <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1954,67 +1954,67 @@
         <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
         <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
         <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="n">
         <v>100</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>90</v>
       </c>
       <c r="AJ8" t="n">
         <v>19</v>
       </c>
       <c r="AK8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL8" t="n">
         <v>42</v>
@@ -2023,75 +2023,75 @@
         <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>130</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
         <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,120 +2101,120 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>4.4</v>
+        <v>1.49</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="G10" t="n">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2336,13 +2336,13 @@
         <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R10" t="n">
         <v>1.23</v>
@@ -2351,67 +2351,67 @@
         <v>4.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.28</v>
+        <v>1.72</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AL10" t="n">
         <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2420,66 +2420,66 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>14</v>
       </c>
-      <c r="AR10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AW10" t="n">
         <v>5.7</v>
       </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AX10" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>1.77</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
         <v>4.4</v>
       </c>
-      <c r="J11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.02</v>
-      </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X11" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN11" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY11" t="n">
         <v>9</v>
       </c>
-      <c r="AR11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>5.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.65</v>
+        <v>6.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>140</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,66 +2683,66 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M12" t="n">
         <v>1.02</v>
       </c>
-      <c r="K12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
         <v>1.02</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -2751,123 +2751,123 @@
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2918,25 +2918,25 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,201 +3054,589 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-30 07:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-30 07:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G16" t="n">
         <v>1.82</v>
       </c>
-      <c r="H14" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="H16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I16" t="n">
         <v>6.8</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>3.55</v>
       </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="K16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M16" t="n">
         <v>1.08</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N16" t="n">
         <v>3.15</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="O16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="Q16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.27</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX16" t="n">
         <v>3.9</v>
       </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X14" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="AY16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB16" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BF14" t="n">
+      <c r="BC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF16" t="n">
         <v>10.5</v>
       </c>
-      <c r="BG14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-03-30 04:58:23</t>
+      <c r="BG16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G2" t="n">
         <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,10 +781,10 @@
         <v>1.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P2" t="n">
         <v>1.47</v>
@@ -796,25 +796,25 @@
         <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
         <v>7.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
@@ -832,46 +832,46 @@
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AO2" t="n">
         <v>32</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>230</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>46</v>
       </c>
       <c r="AP2" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS2" t="n">
         <v>17</v>
@@ -880,7 +880,7 @@
         <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -892,7 +892,7 @@
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AZ2" t="n">
         <v>21</v>
@@ -901,7 +901,7 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC2" t="n">
         <v>36</v>
@@ -910,17 +910,17 @@
         <v>42</v>
       </c>
       <c r="BE2" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="BF2" t="n">
         <v>44</v>
       </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -978,40 +978,40 @@
         <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA3" t="n">
         <v>42</v>
@@ -1023,13 +1023,13 @@
         <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1044,31 +1044,31 @@
         <v>50</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1080,41 +1080,41 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
       </c>
       <c r="BC3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BF3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BG3" t="n">
         <v>22</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
         <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
         <v>1.9</v>
       </c>
       <c r="X4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z4" t="n">
         <v>29</v>
       </c>
       <c r="AA4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="n">
         <v>25</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
         <v>14.5</v>
       </c>
       <c r="AW4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BF4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>13</v>
-      </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -1372,7 +1372,7 @@
         <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
         <v>1.43</v>
@@ -1381,7 +1381,7 @@
         <v>2.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
         <v>2.36</v>
@@ -1390,7 +1390,7 @@
         <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
         <v>17</v>
@@ -1399,7 +1399,7 @@
         <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AA5" t="n">
         <v>44</v>
@@ -1411,28 +1411,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG5" t="n">
         <v>970</v>
       </c>
-      <c r="AG5" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
         <v>55</v>
@@ -1441,68 +1441,68 @@
         <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.6</v>
       </c>
-      <c r="AS5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.34</v>
       </c>
       <c r="G6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -1575,7 +1575,7 @@
         <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>1.84</v>
@@ -1584,13 +1584,13 @@
         <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="X6" t="n">
         <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z6" t="n">
         <v>120</v>
@@ -1599,7 +1599,7 @@
         <v>440</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>15</v>
@@ -1611,10 +1611,10 @@
         <v>190</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>34</v>
@@ -1623,13 +1623,13 @@
         <v>160</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
         <v>18</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
         <v>180</v>
@@ -1641,62 +1641,62 @@
         <v>250</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>3.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.4</v>
+        <v>3.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
         <v>2.16</v>
@@ -1736,16 +1736,16 @@
         <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -1763,7 +1763,7 @@
         <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
         <v>2.92</v>
@@ -1775,7 +1775,7 @@
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
         <v>1.9</v>
@@ -1784,113 +1784,113 @@
         <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z7" t="n">
         <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
         <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
         <v>85</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>22</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1927,103 +1927,103 @@
         <v>1.84</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
         <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
         <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
         <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
         <v>2.18</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y8" t="n">
         <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="n">
         <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
         <v>24</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AO8" t="n">
         <v>130</v>
@@ -2035,10 +2035,10 @@
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2050,10 +2050,10 @@
         <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
@@ -2062,7 +2062,7 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB8" t="n">
         <v>16.5</v>
@@ -2071,20 +2071,20 @@
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2106,68 +2106,68 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.24</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X9" t="n">
         <v>1000</v>
       </c>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,184 +2295,184 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="H10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.75</v>
       </c>
-      <c r="I10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG10" t="n">
         <v>70</v>
       </c>
-      <c r="AF10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>1.77</v>
+        <v>2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,16 +2527,16 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
@@ -2545,135 +2545,135 @@
         <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="X11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AJ11" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
         <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV11" t="n">
         <v>14</v>
       </c>
-      <c r="AR11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.7</v>
+        <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,60 +2683,60 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Club 2 de Mayo de Pedro Juan Cab</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2751,123 +2751,123 @@
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.48</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>1.48</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,60 +3071,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3139,116 +3139,116 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -3265,72 +3265,72 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.02</v>
       </c>
-      <c r="K15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.37</v>
-      </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,201 +3442,589 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:10:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>950</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:10:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
         <v>1.68</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G18" t="n">
         <v>1.82</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H18" t="n">
         <v>5.7</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" t="n">
         <v>6.8</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>3.55</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" t="n">
         <v>4.1</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
         <v>1.08</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" t="n">
         <v>3.15</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X16" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
+      <c r="AU18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV18" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT16" t="n">
+      <c r="AW18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX18" t="n">
         <v>3.55</v>
       </c>
-      <c r="AU16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV16" t="n">
+      <c r="AY18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE18" t="n">
         <v>5</v>
       </c>
-      <c r="AW16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG18" t="n">
         <v>5</v>
       </c>
-      <c r="BD16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-03-30 07:03:50</t>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G2" t="n">
         <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
         <v>1.15</v>
@@ -784,34 +784,34 @@
         <v>2.46</v>
       </c>
       <c r="O2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P2" t="n">
         <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="T2" t="n">
         <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
         <v>6.2</v>
@@ -826,7 +826,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
@@ -838,10 +838,10 @@
         <v>36</v>
       </c>
       <c r="AG2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -859,7 +859,7 @@
         <v>350</v>
       </c>
       <c r="AN2" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
@@ -868,7 +868,7 @@
         <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR2" t="n">
         <v>9.4</v>
@@ -889,38 +889,38 @@
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
         <v>42</v>
       </c>
       <c r="BC2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE2" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="BF2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BG2" t="n">
         <v>19</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -981,31 +981,31 @@
         <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
@@ -1044,7 +1044,7 @@
         <v>50</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
         <v>48</v>
@@ -1065,7 +1065,7 @@
         <v>9.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS3" t="n">
         <v>34</v>
@@ -1080,7 +1080,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX3" t="n">
         <v>17.5</v>
@@ -1095,7 +1095,7 @@
         <v>14.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC3" t="n">
         <v>30</v>
@@ -1104,7 +1104,7 @@
         <v>15</v>
       </c>
       <c r="BE3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF3" t="n">
         <v>27</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G4" t="n">
         <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
@@ -1178,22 +1178,22 @@
         <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W4" t="n">
         <v>1.9</v>
@@ -1205,7 +1205,7 @@
         <v>19.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
         <v>75</v>
@@ -1214,16 +1214,16 @@
         <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
         <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1235,7 +1235,7 @@
         <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1244,10 +1244,10 @@
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1259,19 +1259,19 @@
         <v>15.5</v>
       </c>
       <c r="AR4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10</v>
-      </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW4" t="n">
         <v>11</v>
@@ -1280,7 +1280,7 @@
         <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>15</v>
@@ -1289,26 +1289,26 @@
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>11.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
         <v>3.2</v>
@@ -1348,7 +1348,7 @@
         <v>2.62</v>
       </c>
       <c r="I5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -1357,7 +1357,7 @@
         <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1372,10 +1372,10 @@
         <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
         <v>2.92</v>
@@ -1396,7 +1396,7 @@
         <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>23</v>
@@ -1405,7 +1405,7 @@
         <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
@@ -1414,10 +1414,10 @@
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
@@ -1429,80 +1429,80 @@
         <v>38</v>
       </c>
       <c r="AJ5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
         <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AO5" t="n">
         <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>1.34</v>
       </c>
       <c r="G6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
         <v>13</v>
@@ -1551,7 +1551,7 @@
         <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1566,7 +1566,7 @@
         <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
@@ -1641,10 +1641,10 @@
         <v>250</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AR6" t="n">
         <v>4.1</v>
@@ -1653,34 +1653,34 @@
         <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
         <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
         <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD6" t="n">
         <v>3.95</v>
@@ -1689,14 +1689,14 @@
         <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
         <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
@@ -1745,7 +1745,7 @@
         <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -1757,13 +1757,13 @@
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
         <v>2.92</v>
@@ -1775,7 +1775,7 @@
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.9</v>
@@ -1787,7 +1787,7 @@
         <v>19</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
         <v>85</v>
@@ -1796,13 +1796,13 @@
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="n">
         <v>16.5</v>
@@ -1817,80 +1817,80 @@
         <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
         <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
         <v>85</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
         <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,25 +1945,25 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
         <v>1.92</v>
@@ -1972,119 +1972,119 @@
         <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
         <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
         <v>15.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP8" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB8" t="n">
         <v>16.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="G9" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I9" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="J9" t="n">
         <v>2.88</v>
@@ -2136,37 +2136,37 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="W9" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2235,13 +2235,13 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
@@ -2274,11 +2274,11 @@
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J10" t="n">
         <v>2.78</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.78</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.65</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2468,11 +2468,11 @@
         <v>22</v>
       </c>
       <c r="BG10" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
         <v>3.75</v>
@@ -2554,49 +2554,49 @@
         <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
         <v>70</v>
       </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL11" t="n">
         <v>60</v>
@@ -2608,7 +2608,7 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
         <v>9.199999999999999</v>
@@ -2617,10 +2617,10 @@
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
@@ -2632,7 +2632,7 @@
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -2644,29 +2644,29 @@
         <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.3</v>
+        <v>55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O12" t="n">
         <v>1.48</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2897,10 +2897,10 @@
         <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>3.55</v>
@@ -2909,7 +2909,7 @@
         <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
@@ -2918,7 +2918,7 @@
         <v>2.88</v>
       </c>
       <c r="O13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
         <v>1.64</v>
@@ -2951,7 +2951,7 @@
         <v>17.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
         <v>260</v>
@@ -2960,7 +2960,7 @@
         <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
@@ -2969,7 +2969,7 @@
         <v>150</v>
       </c>
       <c r="AF13" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -2993,7 +2993,7 @@
         <v>240</v>
       </c>
       <c r="AN13" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,10 +3005,10 @@
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
@@ -3017,10 +3017,10 @@
         <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.1</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
@@ -3029,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>15</v>
@@ -3041,20 +3041,20 @@
         <v>18.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.6</v>
+        <v>42</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
         <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G15" t="n">
         <v>3.1</v>
@@ -3291,37 +3291,37 @@
         <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K15" t="n">
         <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="P15" t="n">
         <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.48</v>
+        <v>2.32</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U15" t="n">
         <v>1.62</v>
@@ -3330,7 +3330,7 @@
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,34 +3691,34 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3879,28 +3879,28 @@
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
         <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R18" t="n">
         <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
         <v>2.02</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ18" t="n">
         <v>4.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW18" t="n">
         <v>5</v>
       </c>
-      <c r="AT18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV18" t="n">
+      <c r="AX18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC18" t="n">
         <v>4.3</v>
       </c>
-      <c r="AW18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -763,10 +763,10 @@
         <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
@@ -784,13 +784,13 @@
         <v>2.46</v>
       </c>
       <c r="O2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P2" t="n">
         <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="R2" t="n">
         <v>1.16</v>
@@ -889,16 +889,16 @@
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
         <v>42</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.92</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H3" t="n">
         <v>2.62</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -1002,7 +1002,7 @@
         <v>1.58</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1020,7 +1020,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
@@ -1029,7 +1029,7 @@
         <v>30</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -1056,13 +1056,13 @@
         <v>32</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR3" t="n">
         <v>15.5</v>
@@ -1092,29 +1092,29 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC3" t="n">
         <v>30</v>
       </c>
       <c r="BD3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BF3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I4" t="n">
         <v>3.75</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="J4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1178,13 +1178,13 @@
         <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.69</v>
@@ -1193,16 +1193,16 @@
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
         <v>28</v>
@@ -1211,16 +1211,16 @@
         <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="n">
         <v>14.5</v>
@@ -1247,7 +1247,7 @@
         <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1259,25 +1259,25 @@
         <v>15.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
@@ -1286,29 +1286,29 @@
         <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC4" t="n">
         <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
         <v>12</v>
       </c>
       <c r="BF4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="H5" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -1363,34 +1363,34 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
         <v>1.81</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
         <v>2.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
         <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
         <v>17</v>
@@ -1399,7 +1399,7 @@
         <v>970</v>
       </c>
       <c r="Z5" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
         <v>44</v>
@@ -1432,7 +1432,7 @@
         <v>50</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
         <v>48</v>
@@ -1447,31 +1447,31 @@
         <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AT5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX5" t="n">
         <v>5.6</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
@@ -1480,29 +1480,29 @@
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.7</v>
       </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G6" t="n">
         <v>1.4</v>
@@ -1590,7 +1590,7 @@
         <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z6" t="n">
         <v>120</v>
@@ -1614,7 +1614,7 @@
         <v>10.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>34</v>
@@ -1644,13 +1644,13 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT6" t="n">
         <v>6.8</v>
@@ -1662,7 +1662,7 @@
         <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX6" t="n">
         <v>6.4</v>
@@ -1674,7 +1674,7 @@
         <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
         <v>8.4</v>
@@ -1683,20 +1683,20 @@
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
         <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
         <v>4.3</v>
@@ -1742,7 +1742,7 @@
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -1784,13 +1784,13 @@
         <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="n">
         <v>11.5</v>
@@ -1805,7 +1805,7 @@
         <v>46</v>
       </c>
       <c r="AF7" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
@@ -1820,7 +1820,7 @@
         <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -1841,22 +1841,22 @@
         <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="AX7" t="n">
         <v>11</v>
@@ -1868,29 +1868,29 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
         <v>6.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>15.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
         <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,13 +1945,13 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
         <v>2.1</v>
@@ -1960,34 +1960,34 @@
         <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Z8" t="n">
         <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
@@ -1996,10 +1996,10 @@
         <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
@@ -2011,7 +2011,7 @@
         <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK8" t="n">
         <v>20</v>
@@ -2020,10 +2020,10 @@
         <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO8" t="n">
         <v>120</v>
@@ -2035,10 +2035,10 @@
         <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2047,10 +2047,10 @@
         <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -2062,29 +2062,29 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC8" t="n">
         <v>17.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="I9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2.24</v>
       </c>
-      <c r="J9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="R9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS9" t="n">
         <v>3.9</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.9</v>
+        <v>2.04</v>
       </c>
       <c r="AV9" t="n">
         <v>8.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.68</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BG9" t="n">
-        <v>17.5</v>
+        <v>1.63</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
         <v>2.78</v>
@@ -2327,152 +2327,152 @@
         <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="O10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>4.8</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="BA10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG10" t="n">
         <v>1.73</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
         <v>3.75</v>
@@ -2527,7 +2527,7 @@
         <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O11" t="n">
         <v>1.46</v>
@@ -2554,16 +2554,16 @@
         <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X11" t="n">
         <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2575,7 +2575,7 @@
         <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
         <v>70</v>
@@ -2617,10 +2617,10 @@
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT11" t="n">
         <v>6.6</v>
@@ -2632,7 +2632,7 @@
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -2644,19 +2644,19 @@
         <v>18.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD11" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2721,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="O12" t="n">
         <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -2748,7 +2748,7 @@
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.44</v>
@@ -2939,10 +2939,10 @@
         <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X13" t="n">
         <v>12.5</v>
@@ -2954,7 +2954,7 @@
         <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB13" t="n">
         <v>7.2</v>
@@ -2966,7 +2966,7 @@
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF13" t="n">
         <v>9.6</v>
@@ -2981,7 +2981,7 @@
         <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -3005,7 +3005,7 @@
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS13" t="n">
         <v>7.2</v>
@@ -3017,10 +3017,10 @@
         <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>5.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
@@ -3032,7 +3032,7 @@
         <v>6</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
         <v>15</v>
@@ -3044,17 +3044,17 @@
         <v>42</v>
       </c>
       <c r="BE13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF13" t="n">
         <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3282,55 +3282,55 @@
         <v>2.58</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
         <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J15" t="n">
         <v>2.68</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
         <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
         <v>1.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.05</v>
+        <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>1.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="J17" t="n">
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,19 +3691,19 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>1.38</v>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q17" t="n">
         <v>1.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
         <v>2.62</v>
@@ -3715,10 +3715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3775,52 +3775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="G18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
         <v>5.7</v>
@@ -3876,10 +3876,10 @@
         <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -3909,7 +3909,7 @@
         <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W18" t="n">
         <v>2.22</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -763,7 +763,7 @@
         <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
         <v>2.1</v>
@@ -781,7 +781,7 @@
         <v>1.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
         <v>1.63</v>
@@ -793,7 +793,7 @@
         <v>2.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
         <v>6.6</v>
@@ -808,13 +808,13 @@
         <v>1.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
@@ -826,13 +826,13 @@
         <v>11.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="n">
         <v>36</v>
@@ -868,13 +868,13 @@
         <v>7.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
         <v>9.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
         <v>18</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB2" t="n">
         <v>42</v>
@@ -916,11 +916,11 @@
         <v>46</v>
       </c>
       <c r="BG2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G3" t="n">
         <v>2.92</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.05</v>
-      </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -999,19 +999,19 @@
         <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
         <v>42</v>
@@ -1023,10 +1023,10 @@
         <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
         <v>19</v>
@@ -1053,10 +1053,10 @@
         <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
@@ -1083,38 +1083,38 @@
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>16</v>
       </c>
       <c r="BA3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE3" t="n">
         <v>15.5</v>
       </c>
-      <c r="BB3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>16</v>
-      </c>
       <c r="BF3" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
         <v>23</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.12</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.16</v>
-      </c>
       <c r="H4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.75</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.8</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
@@ -1175,7 +1175,7 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
         <v>1.79</v>
@@ -1184,22 +1184,22 @@
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y4" t="n">
         <v>17</v>
@@ -1214,13 +1214,13 @@
         <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
         <v>14.5</v>
@@ -1244,7 +1244,7 @@
         <v>32</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
         <v>13.5</v>
@@ -1253,10 +1253,10 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
@@ -1265,7 +1265,7 @@
         <v>12.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
         <v>7.8</v>
@@ -1274,22 +1274,22 @@
         <v>13.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
         <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC4" t="n">
         <v>18.5</v>
@@ -1298,17 +1298,17 @@
         <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF4" t="n">
         <v>12</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
         <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T5" t="n">
         <v>1.6</v>
@@ -1393,7 +1393,7 @@
         <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1402,7 +1402,7 @@
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
@@ -1414,7 +1414,7 @@
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
         <v>970</v>
@@ -1423,7 +1423,7 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AI5" t="n">
         <v>38</v>
@@ -1435,7 +1435,7 @@
         <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
         <v>70</v>
@@ -1447,13 +1447,13 @@
         <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS5" t="n">
         <v>30</v>
@@ -1462,47 +1462,47 @@
         <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6</v>
       </c>
-      <c r="BD5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="AW6" t="n">
         <v>4.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G7" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
         <v>1.81</v>
@@ -1930,13 +1930,13 @@
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,7 +1945,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.37</v>
@@ -1954,19 +1954,19 @@
         <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
         <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
@@ -1987,7 +1987,7 @@
         <v>160</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
@@ -2011,19 +2011,19 @@
         <v>95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
         <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>120</v>
@@ -2035,10 +2035,10 @@
         <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2050,7 +2050,7 @@
         <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX8" t="n">
         <v>9</v>
@@ -2062,7 +2062,7 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB8" t="n">
         <v>16</v>
@@ -2074,17 +2074,17 @@
         <v>11</v>
       </c>
       <c r="BE8" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
         <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="I9" t="n">
         <v>2.1</v>
@@ -2130,19 +2130,19 @@
         <v>2.92</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
         <v>2.18</v>
       </c>
       <c r="O9" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
         <v>1.43</v>
@@ -2157,10 +2157,10 @@
         <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.9</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
         <v>2.26</v>
       </c>
       <c r="H10" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
         <v>5.5</v>
@@ -2333,28 +2333,28 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
         <v>1.22</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -2662,11 +2662,11 @@
         <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>55</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -2903,10 +2903,10 @@
         <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.44</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
@@ -3309,7 +3309,7 @@
         <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q15" t="n">
         <v>2.28</v>
@@ -3321,16 +3321,16 @@
         <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
         <v>3.4</v>
@@ -3715,10 +3715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -3876,10 +3876,10 @@
         <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J2" t="n">
         <v>3.15</v>
@@ -778,10 +778,10 @@
         <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O2" t="n">
         <v>1.63</v>
@@ -805,16 +805,16 @@
         <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
         <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
@@ -832,7 +832,7 @@
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
         <v>36</v>
@@ -874,13 +874,13 @@
         <v>9.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
@@ -889,7 +889,7 @@
         <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AY2" t="n">
         <v>18</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>2.82</v>
       </c>
       <c r="G3" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -999,10 +999,10 @@
         <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
@@ -1011,7 +1011,7 @@
         <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
         <v>42</v>
@@ -1041,7 +1041,7 @@
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK3" t="n">
         <v>34</v>
@@ -1056,22 +1056,22 @@
         <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
         <v>34</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
@@ -1092,29 +1092,29 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC3" t="n">
         <v>29</v>
       </c>
       <c r="BD3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
         <v>23</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1175,13 +1175,13 @@
         <v>1.27</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
         <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1190,40 +1190,40 @@
         <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1235,7 +1235,7 @@
         <v>48</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>21</v>
@@ -1247,22 +1247,22 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS4" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>12.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1271,44 +1271,44 @@
         <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>14.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H5" t="n">
         <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -1357,43 +1357,43 @@
         <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="V5" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
         <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
         <v>970</v>
@@ -1408,101 +1408,101 @@
         <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF5" t="n">
         <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AI5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="n">
         <v>38</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>44</v>
-      </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN5" t="n">
         <v>970</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.22</v>
@@ -1575,7 +1575,7 @@
         <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
         <v>1.84</v>
@@ -1593,10 +1593,10 @@
         <v>40</v>
       </c>
       <c r="Z6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA6" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AB6" t="n">
         <v>11</v>
@@ -1632,7 +1632,7 @@
         <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
         <v>6.8</v>
@@ -1644,10 +1644,10 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS6" t="n">
         <v>4.4</v>
@@ -1659,7 +1659,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AW6" t="n">
         <v>4.3</v>
@@ -1680,10 +1680,10 @@
         <v>8.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
         <v>4.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -1775,10 +1775,10 @@
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X7" t="n">
         <v>21</v>
@@ -1796,7 +1796,7 @@
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
         <v>18</v>
@@ -1808,13 +1808,13 @@
         <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
@@ -1826,13 +1826,13 @@
         <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
@@ -1841,7 +1841,7 @@
         <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS7" t="n">
         <v>6.4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>1.77</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1954,7 +1954,7 @@
         <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
         <v>1.32</v>
@@ -1984,16 +1984,16 @@
         <v>44</v>
       </c>
       <c r="AA8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>85</v>
@@ -2008,7 +2008,7 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>22</v>
@@ -2020,7 +2020,7 @@
         <v>46</v>
       </c>
       <c r="AM8" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
         <v>14</v>
@@ -2038,7 +2038,7 @@
         <v>34</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2071,20 +2071,20 @@
         <v>17.5</v>
       </c>
       <c r="BD8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE8" t="n">
         <v>11</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10</v>
       </c>
       <c r="BF8" t="n">
         <v>11.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2115,46 +2115,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="T9" t="n">
         <v>1.5</v>
@@ -2163,10 +2163,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.56</v>
+        <v>2.74</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
         <v>8.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.9</v>
+        <v>2.28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.64</v>
+        <v>2.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.72</v>
+        <v>2.44</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
         <v>2.26</v>
@@ -2318,13 +2318,13 @@
         <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>1.51</v>
@@ -2333,7 +2333,7 @@
         <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O10" t="n">
         <v>1.53</v>
@@ -2357,7 +2357,7 @@
         <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
         <v>1.79</v>
@@ -2417,7 +2417,7 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ10" t="n">
         <v>4</v>
@@ -2426,53 +2426,53 @@
         <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV10" t="n">
         <v>4.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ10" t="n">
         <v>4.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
         <v>5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.73</v>
+        <v>1.32</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>3.75</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
@@ -2551,7 +2551,7 @@
         <v>1.85</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
         <v>1.75</v>
@@ -2605,7 +2605,7 @@
         <v>180</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2662,11 +2662,11 @@
         <v>19.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
         <v>6.8</v>
@@ -2969,7 +2969,7 @@
         <v>140</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG13" t="n">
         <v>11</v>
@@ -3005,10 +3005,10 @@
         <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT13" t="n">
         <v>5.6</v>
@@ -3017,10 +3017,10 @@
         <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
         <v>7.8</v>
@@ -3029,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
         <v>15</v>
@@ -3044,17 +3044,17 @@
         <v>42</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
         <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         <v>1.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="S14" t="n">
         <v>1.02</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>2.58</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H15" t="n">
         <v>3.15</v>
@@ -3327,10 +3327,10 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3497,13 +3497,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
         <v>1.37</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G17" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="H17" t="n">
         <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3706,7 +3706,7 @@
         <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -3715,10 +3715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>5.3</v>
       </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.92</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,133 +942,133 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.82</v>
+        <v>4.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.82</v>
+        <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.82</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="V3" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
         <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH3" t="n">
         <v>32</v>
       </c>
-      <c r="AF3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS3" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>34</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1077,44 +1077,44 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG3" t="n">
         <v>27</v>
       </c>
-      <c r="AX3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>23</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.84</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>2.72</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.75</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA4" t="n">
         <v>20</v>
       </c>
-      <c r="Z4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="BB4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE4" t="n">
         <v>44</v>
       </c>
-      <c r="AF4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BF4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.66</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
-        <v>2.82</v>
+        <v>3.95</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF5" t="n">
         <v>14</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR5" t="n">
         <v>26</v>
       </c>
-      <c r="AF5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AS5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AI5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ5" t="n">
+      <c r="AW5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA5" t="n">
         <v>42</v>
       </c>
-      <c r="AK5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="BB5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG5" t="n">
         <v>13.5</v>
       </c>
-      <c r="AU5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4</v>
+        <v>2.66</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>2.84</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>2.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="X6" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
-        <v>430</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>11</v>
       </c>
-      <c r="AC6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>2.08</v>
+        <v>1.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="I7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>540</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>430</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>470</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW7" t="n">
         <v>4.4</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AX7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="BA7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BD7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE7" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="G8" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO8" t="n">
         <v>44</v>
       </c>
-      <c r="AA8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="AP8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>10</v>
       </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG8" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>1.82</v>
       </c>
       <c r="H9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.85</v>
       </c>
-      <c r="I9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>500</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.96</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.8</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.74</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.3</v>
+        <v>13.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.36</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.28</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.3</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.46</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.44</v>
+        <v>17.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.44</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.89</v>
+        <v>14.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.46</v>
+        <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.26</v>
+        <v>18</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -2300,67 +2300,67 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I10" t="n">
         <v>2.06</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.26</v>
       </c>
-      <c r="H10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="R10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.11</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.71</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="W10" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2378,7 +2378,7 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
@@ -2417,69 +2417,69 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.38</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="BB10" t="n">
-        <v>5</v>
+        <v>1.72</v>
       </c>
       <c r="BC10" t="n">
-        <v>5</v>
+        <v>2.64</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.4</v>
+        <v>1.72</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>5</v>
+        <v>1.73</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.32</v>
+        <v>5.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X11" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR11" t="n">
         <v>4.1</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AS11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>3.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>8.6</v>
+        <v>1.95</v>
       </c>
       <c r="BB11" t="n">
         <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.4</v>
+        <v>2.74</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>2.16</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>2.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>55</v>
+        <v>1.94</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Juan Cab</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Club 2 de Mayo de Pedro Juan Cab</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>4.3</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>2.32</v>
+        <v>1.31</v>
       </c>
       <c r="X13" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="H14" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S14" t="n">
         <v>4.4</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.02</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF14" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>970</v>
-      </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AJ14" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW14" t="n">
         <v>9</v>
       </c>
-      <c r="AR14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.6</v>
+        <v>42</v>
       </c>
       <c r="BE14" t="n">
-        <v>140</v>
+        <v>9.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,60 +3265,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" t="n">
         <v>2.96</v>
       </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>3.15</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>1.02</v>
       </c>
       <c r="R15" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="S15" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -3327,129 +3327,129 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,22 +3497,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>1.37</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3521,10 +3521,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,69 +3581,69 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,22 +3691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>1.37</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -3715,10 +3715,10 @@
         <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,201 +3830,395 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>19</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Tolima</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Aguilas Doradas</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>1.72</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>1.81</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H19" t="n">
         <v>5.7</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>6.8</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>3.55</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K19" t="n">
         <v>4.1</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="L19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M19" t="n">
         <v>1.08</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>3.15</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>1.39</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>1.74</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>2.14</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1.27</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>4</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2.02</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1.8</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>1.18</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>2.22</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>970</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC19" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD19" t="n">
         <v>950</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG19" t="n">
         <v>12</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AH19" t="n">
         <v>950</v>
       </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>970</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK19" t="n">
         <v>24</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AL19" t="n">
         <v>55</v>
       </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AQ19" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AR19" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AS19" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AT19" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AU19" t="n">
         <v>3.4</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AV19" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AW19" t="n">
         <v>5</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AX19" t="n">
         <v>3.6</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AY19" t="n">
         <v>3.65</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="AZ19" t="n">
         <v>4.4</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BA19" t="n">
         <v>5</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BB19" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BC19" t="n">
         <v>4.3</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BD19" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BE19" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BF19" t="n">
         <v>10.5</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BG19" t="n">
         <v>5.1</v>
       </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-03-30 17:34:08</t>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,145 +757,145 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.56</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
         <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="M3" t="n">
         <v>1.14</v>
@@ -978,7 +978,7 @@
         <v>2.44</v>
       </c>
       <c r="O3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P3" t="n">
         <v>1.47</v>
@@ -987,7 +987,7 @@
         <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
         <v>6.6</v>
@@ -1008,7 +1008,7 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z3" t="n">
         <v>10.5</v>
@@ -1029,7 +1029,7 @@
         <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
         <v>22</v>
@@ -1044,7 +1044,7 @@
         <v>700</v>
       </c>
       <c r="AK3" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AL3" t="n">
         <v>700</v>
@@ -1056,7 +1056,7 @@
         <v>700</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
         <v>7.2</v>
@@ -1065,7 +1065,7 @@
         <v>5.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS3" t="n">
         <v>17.5</v>
@@ -1077,31 +1077,31 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
         <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
         <v>42</v>
       </c>
       <c r="BC3" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BD3" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="BE3" t="n">
         <v>110</v>
@@ -1110,11 +1110,11 @@
         <v>46</v>
       </c>
       <c r="BG3" t="n">
-        <v>27</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1172,13 +1172,13 @@
         <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
@@ -1187,7 +1187,7 @@
         <v>3.75</v>
       </c>
       <c r="T4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
         <v>2.12</v>
@@ -1199,7 +1199,7 @@
         <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
         <v>11</v>
@@ -1211,7 +1211,7 @@
         <v>42</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
@@ -1223,7 +1223,7 @@
         <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>13</v>
@@ -1232,7 +1232,7 @@
         <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ4" t="n">
         <v>44</v>
@@ -1244,13 +1244,13 @@
         <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO4" t="n">
         <v>29</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>28</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
@@ -1259,13 +1259,13 @@
         <v>10</v>
       </c>
       <c r="AR4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
@@ -1274,7 +1274,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX4" t="n">
         <v>16.5</v>
@@ -1301,14 +1301,14 @@
         <v>44</v>
       </c>
       <c r="BF4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>3.85</v>
       </c>
       <c r="I5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
@@ -1378,7 +1378,7 @@
         <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
         <v>1.7</v>
@@ -1387,19 +1387,19 @@
         <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
         <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
         <v>160</v>
@@ -1411,7 +1411,7 @@
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>42</v>
@@ -1426,7 +1426,7 @@
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
         <v>24</v>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>15.5</v>
@@ -1456,13 +1456,13 @@
         <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
         <v>14.5</v>
@@ -1477,7 +1477,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
         <v>42</v>
@@ -1486,23 +1486,23 @@
         <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF5" t="n">
         <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1536,40 +1536,40 @@
         <v>2.66</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
         <v>2.48</v>
@@ -1581,16 +1581,16 @@
         <v>2.52</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Z6" t="n">
         <v>50</v>
@@ -1605,13 +1605,13 @@
         <v>8.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AG6" t="n">
         <v>17.5</v>
@@ -1620,13 +1620,13 @@
         <v>14.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>85</v>
@@ -1635,37 +1635,37 @@
         <v>320</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>14.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>19.5</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
@@ -1674,29 +1674,29 @@
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>9.4</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
         <v>5.1</v>
@@ -1775,122 +1775,122 @@
         <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
         <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="n">
         <v>540</v>
       </c>
       <c r="AA7" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AE7" t="n">
         <v>190</v>
       </c>
       <c r="AF7" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="n">
         <v>470</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AM7" t="n">
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO7" t="n">
         <v>250</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AV7" t="n">
         <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7" t="n">
         <v>12.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
         <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1921,31 +1921,31 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="G8" t="n">
         <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.25</v>
@@ -1954,137 +1954,137 @@
         <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
         <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.98</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AA8" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO8" t="n">
         <v>46</v>
       </c>
-      <c r="AF8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>44</v>
-      </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
       </c>
       <c r="AY8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>9</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q9" t="n">
         <v>2.1</v>
@@ -2154,16 +2154,16 @@
         <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
         <v>2.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
         <v>2.2</v>
@@ -2181,7 +2181,7 @@
         <v>150</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
         <v>8.6</v>
@@ -2190,7 +2190,7 @@
         <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="n">
         <v>10</v>
@@ -2202,28 +2202,28 @@
         <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK9" t="n">
         <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
         <v>15</v>
@@ -2232,7 +2232,7 @@
         <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2244,10 +2244,10 @@
         <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9" t="n">
         <v>9.4</v>
@@ -2256,29 +2256,29 @@
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2309,52 +2309,52 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>1.85</v>
       </c>
       <c r="I10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.49</v>
       </c>
       <c r="P10" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
         <v>1.96</v>
@@ -2366,7 +2366,7 @@
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2381,7 +2381,7 @@
         <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2426,53 +2426,53 @@
         <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
         <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.69</v>
+        <v>2.22</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="BG10" t="n">
         <v>5.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -2548,7 +2548,7 @@
         <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
         <v>1.25</v>
@@ -2584,7 +2584,7 @@
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2593,7 +2593,7 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -2620,7 +2620,7 @@
         <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AT11" t="n">
         <v>4.2</v>
@@ -2632,7 +2632,7 @@
         <v>6.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AX11" t="n">
         <v>5.8</v>
@@ -2641,32 +2641,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="BB11" t="n">
         <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2730,19 +2730,19 @@
         <v>1.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V12" t="n">
         <v>1.32</v>
@@ -2751,7 +2751,7 @@
         <v>1.75</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
         <v>12</v>
@@ -2760,10 +2760,10 @@
         <v>85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC12" t="n">
         <v>7.8</v>
@@ -2772,10 +2772,10 @@
         <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -2787,34 +2787,34 @@
         <v>380</v>
       </c>
       <c r="AJ12" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AM12" t="n">
-        <v>450</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>26</v>
       </c>
       <c r="AO12" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12" t="n">
         <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
@@ -2823,44 +2823,44 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
         <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
         <v>24</v>
       </c>
       <c r="BD12" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H13" t="n">
         <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O13" t="n">
         <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
         <v>2.36</v>
@@ -2939,13 +2939,13 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="W13" t="n">
         <v>1.31</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y13" t="n">
         <v>1000</v>
@@ -3002,59 +3002,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3124,13 +3124,13 @@
         <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
         <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
@@ -3145,7 +3145,7 @@
         <v>17</v>
       </c>
       <c r="Z14" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>900</v>
@@ -3157,10 +3157,10 @@
         <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AE14" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AF14" t="n">
         <v>9.4</v>
@@ -3169,22 +3169,22 @@
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AI14" t="n">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ14" t="n">
         <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN14" t="n">
         <v>16</v>
@@ -3202,7 +3202,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
         <v>5.6</v>
@@ -3217,16 +3217,16 @@
         <v>9</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB14" t="n">
         <v>15</v>
@@ -3235,20 +3235,20 @@
         <v>18.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
         <v>9.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
         <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
         <v>3.9</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="K16" t="n">
         <v>3.3</v>
@@ -3497,13 +3497,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
         <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q16" t="n">
         <v>2.28</v>
@@ -3521,7 +3521,7 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
         <v>1.54</v>
@@ -3587,16 +3587,16 @@
         <v>1.15</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AS16" t="n">
         <v>1.16</v>
       </c>
       <c r="AT16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AU16" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.13</v>
       </c>
       <c r="AV16" t="n">
         <v>1.15</v>
@@ -3608,13 +3608,13 @@
         <v>1.15</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BB16" t="n">
         <v>1.16</v>
@@ -3626,7 +3626,7 @@
         <v>1.16</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BF16" t="n">
         <v>1.55</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3667,94 +3667,94 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.37</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF17" t="n">
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3772,65 +3772,65 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,7 +3885,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O18" t="n">
         <v>1.35</v>
@@ -3894,10 +3894,10 @@
         <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="S18" t="n">
         <v>2.6</v>
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -4085,10 +4085,10 @@
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
@@ -4103,13 +4103,13 @@
         <v>1.8</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
         <v>2.22</v>
       </c>
       <c r="X19" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
         <v>1000</v>
@@ -4133,7 +4133,7 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
@@ -4151,7 +4151,7 @@
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY19" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV19" t="n">
+      <c r="AZ19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB19" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BC19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD19" t="n">
         <v>5</v>
       </c>
-      <c r="AX19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BE19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
@@ -784,7 +784,7 @@
         <v>2.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
         <v>1.65</v>
@@ -793,28 +793,28 @@
         <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
         <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
         <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>14.5</v>
@@ -865,10 +865,10 @@
         <v>27</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
         <v>9.6</v>
@@ -880,47 +880,47 @@
         <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW2" t="n">
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>60</v>
+        <v>5.6</v>
       </c>
       <c r="BG2" t="n">
         <v>17.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G3" t="n">
         <v>5.2</v>
@@ -996,7 +996,7 @@
         <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V3" t="n">
         <v>1.96</v>
@@ -1005,7 +1005,7 @@
         <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y3" t="n">
         <v>5.9</v>
@@ -1062,7 +1062,7 @@
         <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AR3" t="n">
         <v>9</v>
@@ -1074,19 +1074,19 @@
         <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
         <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -1098,10 +1098,10 @@
         <v>42</v>
       </c>
       <c r="BC3" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="BD3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BE3" t="n">
         <v>110</v>
@@ -1110,11 +1110,11 @@
         <v>46</v>
       </c>
       <c r="BG3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I4" t="n">
         <v>2.8</v>
@@ -1175,7 +1175,7 @@
         <v>1.37</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
         <v>2.08</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
         <v>1.8</v>
@@ -1384,7 +1384,7 @@
         <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
         <v>1.34</v>
@@ -1393,10 +1393,10 @@
         <v>1.91</v>
       </c>
       <c r="X5" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y5" t="n">
         <v>17.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>17</v>
       </c>
       <c r="Z5" t="n">
         <v>29</v>
@@ -1408,7 +1408,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1417,13 +1417,13 @@
         <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>48</v>
@@ -1456,7 +1456,7 @@
         <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1477,22 +1477,22 @@
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
         <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BF5" t="n">
         <v>11.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
         <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>17.5</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
@@ -1650,7 +1650,7 @@
         <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT6" t="n">
         <v>13.5</v>
@@ -1674,19 +1674,19 @@
         <v>11</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
         <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
         <v>13.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.35</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H7" t="n">
         <v>9.4</v>
@@ -1742,10 +1742,10 @@
         <v>5.1</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
@@ -1760,7 +1760,7 @@
         <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
         <v>1.5</v>
@@ -1778,13 +1778,13 @@
         <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="X7" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Y7" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>540</v>
@@ -1793,10 +1793,10 @@
         <v>440</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD7" t="n">
         <v>100</v>
@@ -1811,7 +1811,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="n">
         <v>470</v>
@@ -1829,7 +1829,7 @@
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO7" t="n">
         <v>250</v>
@@ -1841,10 +1841,10 @@
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -1856,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
         <v>7.4</v>
@@ -1868,7 +1868,7 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
         <v>9.800000000000001</v>
@@ -1877,20 +1877,20 @@
         <v>12.5</v>
       </c>
       <c r="BD7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BE7" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -1972,7 +1972,7 @@
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -2023,10 +2023,10 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="AP8" t="n">
         <v>10.5</v>
@@ -2035,10 +2035,10 @@
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
         <v>9</v>
@@ -2050,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2062,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2071,20 +2071,20 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>1.78</v>
       </c>
       <c r="G9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2157,16 +2157,16 @@
         <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
@@ -2220,7 +2220,7 @@
         <v>13</v>
       </c>
       <c r="AO9" t="n">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="AP9" t="n">
         <v>12</v>
@@ -2241,7 +2241,7 @@
         <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
         <v>15.5</v>
@@ -2268,17 +2268,17 @@
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I10" t="n">
         <v>2.04</v>
@@ -2324,10 +2324,10 @@
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M10" t="n">
         <v>1.11</v>
@@ -2336,7 +2336,7 @@
         <v>2.62</v>
       </c>
       <c r="O10" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
         <v>1.54</v>
@@ -2423,10 +2423,10 @@
         <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -2438,41 +2438,41 @@
         <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="AY10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BC10" t="n">
         <v>1.92</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="BG10" t="n">
         <v>5.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
         <v>2.96</v>
@@ -2545,16 +2545,16 @@
         <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X11" t="n">
         <v>90</v>
@@ -2611,16 +2611,16 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="AT11" t="n">
         <v>4.2</v>
@@ -2629,10 +2629,10 @@
         <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AX11" t="n">
         <v>5.8</v>
@@ -2641,32 +2641,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE11" t="n">
         <v>2.98</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.3</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
         <v>1.32</v>
@@ -2799,7 +2799,7 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2912,25 +2912,25 @@
         <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="O13" t="n">
         <v>1.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -2945,116 +2945,116 @@
         <v>1.31</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.12</v>
+        <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.12</v>
+        <v>4.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.12</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.12</v>
+        <v>4.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.12</v>
+        <v>4.4</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.12</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.12</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.12</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.12</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.12</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.12</v>
+        <v>4.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>1.75</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I14" t="n">
         <v>6.8</v>
@@ -3130,7 +3130,7 @@
         <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3476,167 +3476,167 @@
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="H16" t="n">
         <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>160</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BC16" t="n">
         <v>2.28</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BD16" t="n">
-        <v>1.16</v>
+        <v>2.14</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.17</v>
+        <v>1.93</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
         <v>1.89</v>
@@ -3682,7 +3682,7 @@
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.43</v>
@@ -3733,13 +3733,13 @@
         <v>29</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
         <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>25</v>
@@ -3748,13 +3748,13 @@
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH17" t="n">
         <v>23</v>
       </c>
-      <c r="AH17" t="n">
-        <v>26</v>
-      </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3799,7 +3799,7 @@
         <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.2</v>
+        <v>28</v>
       </c>
       <c r="AY17" t="n">
         <v>16</v>
@@ -3808,29 +3808,29 @@
         <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG17" t="n">
         <v>13.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>1.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="H18" t="n">
         <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="J18" t="n">
         <v>3.4</v>
@@ -3885,7 +3885,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="O18" t="n">
         <v>1.35</v>
@@ -3900,19 +3900,19 @@
         <v>1.13</v>
       </c>
       <c r="S18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -4058,22 +4058,22 @@
         <v>1.72</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H19" t="n">
         <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
@@ -4124,7 +4124,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
@@ -4166,13 +4166,13 @@
         <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR19" t="n">
         <v>5.1</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4181,44 +4181,44 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4.6</v>
       </c>
-      <c r="BA19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M2" t="n">
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="W2" t="n">
         <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
         <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
         <v>34</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>120</v>
       </c>
       <c r="AK2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU2" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
         <v>9.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -963,37 +963,37 @@
         <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.65</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.63</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
         <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
         <v>1.64</v>
@@ -1005,13 +1005,13 @@
         <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>26</v>
@@ -1026,10 +1026,10 @@
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="n">
         <v>22</v>
@@ -1038,13 +1038,13 @@
         <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AK3" t="n">
-        <v>700</v>
+        <v>230</v>
       </c>
       <c r="AL3" t="n">
         <v>700</v>
@@ -1056,7 +1056,7 @@
         <v>700</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP3" t="n">
         <v>7.2</v>
@@ -1065,10 +1065,10 @@
         <v>5.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
         <v>10.5</v>
@@ -1080,22 +1080,22 @@
         <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
         <v>19.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BC3" t="n">
         <v>38</v>
@@ -1110,11 +1110,11 @@
         <v>46</v>
       </c>
       <c r="BG3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G4" t="n">
         <v>2.84</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.88</v>
-      </c>
       <c r="H4" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1163,28 +1163,28 @@
         <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1193,13 +1193,13 @@
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
         <v>11</v>
@@ -1208,7 +1208,7 @@
         <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
         <v>11</v>
@@ -1238,7 +1238,7 @@
         <v>44</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL4" t="n">
         <v>48</v>
@@ -1250,7 +1250,7 @@
         <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
@@ -1262,7 +1262,7 @@
         <v>16.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
         <v>28</v>
       </c>
       <c r="AX4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
         <v>11.5</v>
@@ -1286,16 +1286,16 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BC4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BE4" t="n">
         <v>44</v>
@@ -1304,11 +1304,11 @@
         <v>26</v>
       </c>
       <c r="BG4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1339,31 +1339,31 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1375,37 +1375,37 @@
         <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
         <v>8.800000000000001</v>
@@ -1414,25 +1414,25 @@
         <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL5" t="n">
         <v>32</v>
@@ -1441,22 +1441,22 @@
         <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>15.5</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1480,29 +1480,29 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>28</v>
       </c>
       <c r="BE5" t="n">
-        <v>17.5</v>
+        <v>60</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1533,73 +1533,73 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H6" t="n">
         <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="T6" t="n">
         <v>1.53</v>
       </c>
       <c r="U6" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V6" t="n">
         <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X6" t="n">
         <v>30</v>
       </c>
       <c r="Y6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA6" t="n">
         <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="n">
         <v>8.6</v>
@@ -1614,16 +1614,16 @@
         <v>42</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
         <v>14.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
@@ -1635,10 +1635,10 @@
         <v>320</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="AO6" t="n">
-        <v>46</v>
+        <v>17.5</v>
       </c>
       <c r="AP6" t="n">
         <v>10.5</v>
@@ -1650,10 +1650,10 @@
         <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU6" t="n">
         <v>6.6</v>
@@ -1662,7 +1662,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1674,29 +1674,29 @@
         <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
         <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1727,73 +1727,73 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L7" t="n">
         <v>1.35</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.26</v>
-      </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
         <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="T7" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="Z7" t="n">
         <v>540</v>
       </c>
       <c r="AA7" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC7" t="n">
         <v>12.5</v>
@@ -1802,10 +1802,10 @@
         <v>100</v>
       </c>
       <c r="AE7" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
@@ -1820,7 +1820,7 @@
         <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL7" t="n">
         <v>100</v>
@@ -1829,22 +1829,22 @@
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AP7" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -1856,41 +1856,41 @@
         <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>11</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1921,46 +1921,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G8" t="n">
         <v>2.04</v>
       </c>
       <c r="H8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
         <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
         <v>1.67</v>
@@ -1969,7 +1969,7 @@
         <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
         <v>1.96</v>
@@ -1996,7 +1996,7 @@
         <v>30</v>
       </c>
       <c r="AE8" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AF8" t="n">
         <v>25</v>
@@ -2026,7 +2026,7 @@
         <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
         <v>10.5</v>
@@ -2035,10 +2035,10 @@
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
         <v>9</v>
@@ -2050,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2062,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>11.5</v>
@@ -2071,7 +2071,7 @@
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE8" t="n">
         <v>9.800000000000001</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AB9" t="n">
         <v>8</v>
       </c>
       <c r="AC9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX9" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AY9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>21</v>
       </c>
-      <c r="AE9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="BA9" t="n">
+        <v>70</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>20</v>
       </c>
       <c r="BE9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2312,55 +2312,55 @@
         <v>4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="I10" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
         <v>1.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="R10" t="n">
         <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
         <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,7 +2417,7 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
         <v>4.2</v>
@@ -2426,7 +2426,7 @@
         <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
@@ -2438,31 +2438,31 @@
         <v>7.6</v>
       </c>
       <c r="AW10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AY10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>7</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>3.35</v>
+        <v>2.54</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="BF10" t="n">
         <v>1.92</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
         <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
         <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X11" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC11" t="n">
         <v>42</v>
@@ -2617,10 +2617,10 @@
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AT11" t="n">
         <v>4.2</v>
@@ -2629,10 +2629,10 @@
         <v>4.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AX11" t="n">
         <v>5.8</v>
@@ -2641,32 +2641,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2697,70 +2697,70 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="H12" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
         <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
         <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
         <v>8</v>
@@ -2769,28 +2769,28 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
         <v>370</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>380</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
         <v>290</v>
@@ -2799,7 +2799,7 @@
         <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -2808,37 +2808,37 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>48</v>
+        <v>9.6</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
         <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -2847,20 +2847,20 @@
         <v>24</v>
       </c>
       <c r="BD12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2894,55 +2894,55 @@
         <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I13" t="n">
         <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
         <v>3.3</v>
       </c>
       <c r="L13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.52</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.48</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
         <v>10</v>
@@ -2966,40 +2966,40 @@
         <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF13" t="n">
         <v>30</v>
       </c>
       <c r="AG13" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
         <v>75</v>
       </c>
       <c r="AL13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
         <v>100</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>110</v>
       </c>
       <c r="AO13" t="n">
         <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.2</v>
@@ -3008,7 +3008,7 @@
         <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3020,10 +3020,10 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX13" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.4</v>
       </c>
       <c r="AY13" t="n">
         <v>14.5</v>
@@ -3032,29 +3032,29 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF13" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF13" t="n">
-        <v>5</v>
-      </c>
       <c r="BG13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3085,64 +3085,64 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="G14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="R14" t="n">
         <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
         <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
         <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3151,19 +3151,19 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="AE14" t="n">
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
@@ -3175,7 +3175,7 @@
         <v>700</v>
       </c>
       <c r="AJ14" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
         <v>23</v>
@@ -3187,7 +3187,7 @@
         <v>700</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3196,13 +3196,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
         <v>5.6</v>
@@ -3211,22 +3211,22 @@
         <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>7.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>15</v>
@@ -3235,20 +3235,20 @@
         <v>18.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
         <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3473,46 +3473,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
         <v>2.78</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
         <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M16" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O16" t="n">
         <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="T16" t="n">
         <v>2.02</v>
@@ -3587,10 +3587,10 @@
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -3599,10 +3599,10 @@
         <v>5.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AX16" t="n">
         <v>12</v>
@@ -3611,32 +3611,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="BB16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC16" t="n">
         <v>2.3</v>
       </c>
-      <c r="BC16" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3670,58 +3670,58 @@
         <v>4.5</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J17" t="n">
         <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T17" t="n">
         <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V17" t="n">
         <v>1.98</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
         <v>9.199999999999999</v>
@@ -3730,10 +3730,10 @@
         <v>13.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AB17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
         <v>9.4</v>
@@ -3754,7 +3754,7 @@
         <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3778,28 +3778,28 @@
         <v>9.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
         <v>9</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>28</v>
+        <v>4.6</v>
       </c>
       <c r="AY17" t="n">
         <v>16</v>
@@ -3808,29 +3808,29 @@
         <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC17" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3861,46 +3861,46 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="G18" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>15.5</v>
+        <v>870</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -3909,10 +3909,10 @@
         <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.72</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H19" t="n">
         <v>5.7</v>
@@ -4067,34 +4067,34 @@
         <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
         <v>2.02</v>
@@ -4103,13 +4103,13 @@
         <v>1.8</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y19" t="n">
         <v>1000</v>
@@ -4124,7 +4124,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
@@ -4145,7 +4145,7 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4181,44 +4181,44 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -769,7 +769,7 @@
         <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
@@ -814,7 +814,7 @@
         <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z2" t="n">
         <v>13.5</v>
@@ -865,16 +865,16 @@
         <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -883,44 +883,44 @@
         <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>22</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC2" t="n">
         <v>7</v>
       </c>
-      <c r="BC2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -951,43 +951,43 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O3" t="n">
         <v>1.65</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
         <v>6.8</v>
@@ -996,28 +996,28 @@
         <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>7.6</v>
@@ -1026,76 +1026,76 @@
         <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AF3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
         <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
         <v>180</v>
       </c>
       <c r="AK3" t="n">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="AL3" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AN3" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AO3" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>25</v>
       </c>
-      <c r="AY3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>27</v>
-      </c>
       <c r="BA3" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BB3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BC3" t="n">
         <v>38</v>
@@ -1107,14 +1107,14 @@
         <v>110</v>
       </c>
       <c r="BF3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BG3" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="G4" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1163,7 +1163,7 @@
         <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1175,16 +1175,16 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1193,106 +1193,106 @@
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL4" t="n">
         <v>44</v>
       </c>
-      <c r="AK4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>48</v>
-      </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7</v>
       </c>
       <c r="AV4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY4" t="n">
         <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BB4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BD4" t="n">
         <v>23</v>
@@ -1301,14 +1301,14 @@
         <v>44</v>
       </c>
       <c r="BF4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BG4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1339,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.38</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.6</v>
@@ -1369,7 +1369,7 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>1.8</v>
@@ -1381,58 +1381,58 @@
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
         <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
         <v>18</v>
       </c>
       <c r="Z5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
         <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
         <v>13.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AK5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>32</v>
@@ -1441,19 +1441,19 @@
         <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>16.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
         <v>65</v>
@@ -1465,13 +1465,13 @@
         <v>8</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
         <v>38</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
@@ -1486,7 +1486,7 @@
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD5" t="n">
         <v>28</v>
@@ -1495,14 +1495,14 @@
         <v>60</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1533,79 +1533,79 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="U6" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
         <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y6" t="n">
         <v>22</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
         <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
@@ -1614,7 +1614,7 @@
         <v>42</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
         <v>14.5</v>
@@ -1623,10 +1623,10 @@
         <v>95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
         <v>85</v>
@@ -1635,28 +1635,28 @@
         <v>320</v>
       </c>
       <c r="AN6" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>17.5</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
         <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
         <v>11.5</v>
@@ -1665,38 +1665,38 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF6" t="n">
         <v>7</v>
       </c>
-      <c r="BE6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
         <v>1.41</v>
       </c>
       <c r="H7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.73</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.8</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1781,31 +1781,31 @@
         <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
         <v>540</v>
       </c>
       <c r="AA7" t="n">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
@@ -1820,7 +1820,7 @@
         <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>100</v>
@@ -1829,68 +1829,68 @@
         <v>390</v>
       </c>
       <c r="AN7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT7" t="n">
         <v>6.4</v>
       </c>
-      <c r="AO7" t="n">
-        <v>300</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="AU7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AV7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AX7" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB7" t="n">
         <v>10</v>
       </c>
-      <c r="BB7" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.37</v>
@@ -1948,31 +1948,31 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
         <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
         <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U8" t="n">
         <v>2.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X8" t="n">
         <v>26</v>
@@ -1990,7 +1990,7 @@
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
         <v>30</v>
@@ -2026,65 +2026,65 @@
         <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
         <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
         <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
         <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="G9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
         <v>6.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.4</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
@@ -2139,40 +2139,40 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
         <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
         <v>3.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="X9" t="n">
         <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
         <v>48</v>
@@ -2184,16 +2184,16 @@
         <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
         <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AG9" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
         <v>16.5</v>
@@ -2214,10 +2214,10 @@
         <v>40</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
         <v>130</v>
@@ -2229,13 +2229,13 @@
         <v>16.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AS9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
         <v>8</v>
@@ -2250,35 +2250,35 @@
         <v>8.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>16.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2309,70 +2309,70 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="G10" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="H10" t="n">
-        <v>1.89</v>
+        <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="J10" t="n">
         <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
@@ -2417,19 +2417,19 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="AU10" t="n">
         <v>4.9</v>
@@ -2441,38 +2441,38 @@
         <v>7.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.62</v>
+        <v>7.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BD10" t="n">
         <v>2.54</v>
       </c>
-      <c r="BA10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BE10" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="BG10" t="n">
         <v>5.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2503,67 +2503,67 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
         <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
       </c>
       <c r="Y11" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z11" t="n">
         <v>500</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2596,7 +2596,7 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,28 +2611,28 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="AX11" t="n">
         <v>5.8</v>
@@ -2641,32 +2641,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD11" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.4</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
         <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
       </c>
       <c r="Y12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG12" t="n">
         <v>11</v>
       </c>
-      <c r="Z12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>370</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12</v>
-      </c>
       <c r="AH12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN12" t="n">
         <v>22</v>
       </c>
-      <c r="AI12" t="n">
-        <v>380</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>60</v>
-      </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF12" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="BG12" t="n">
         <v>13</v>
       </c>
-      <c r="BC12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H13" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
         <v>2.98</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.57</v>
@@ -2936,10 +2936,10 @@
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W13" t="n">
         <v>1.33</v>
@@ -2951,13 +2951,13 @@
         <v>8.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA13" t="n">
         <v>40</v>
       </c>
       <c r="AB13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
@@ -2969,10 +2969,10 @@
         <v>38</v>
       </c>
       <c r="AF13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH13" t="n">
         <v>26</v>
@@ -2981,25 +2981,25 @@
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
         <v>95</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>100</v>
       </c>
       <c r="AO13" t="n">
         <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.2</v>
@@ -3008,7 +3008,7 @@
         <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3020,10 +3020,10 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
         <v>14.5</v>
@@ -3032,29 +3032,29 @@
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5</v>
       </c>
-      <c r="BB13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
         <v>1.53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O14" t="n">
         <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
         <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="X14" t="n">
         <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Z14" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>260</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>140</v>
       </c>
       <c r="AE14" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH14" t="n">
         <v>48</v>
       </c>
       <c r="AI14" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BB14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BF14" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="G16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I16" t="n">
         <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K16" t="n">
         <v>3.05</v>
@@ -3503,7 +3503,7 @@
         <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
         <v>2.6</v>
@@ -3524,10 +3524,10 @@
         <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="Y16" t="n">
         <v>160</v>
@@ -3560,7 +3560,7 @@
         <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
         <v>900</v>
@@ -3587,10 +3587,10 @@
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -3599,44 +3599,44 @@
         <v>5.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.32</v>
+        <v>1.96</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G17" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I17" t="n">
         <v>1.92</v>
       </c>
-      <c r="I17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.49</v>
@@ -3697,7 +3697,7 @@
         <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
         <v>2.26</v>
@@ -3712,43 +3712,43 @@
         <v>1.96</v>
       </c>
       <c r="U17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="W17" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="X17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z17" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AA17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>25</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AH17" t="n">
         <v>23</v>
@@ -3772,7 +3772,7 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
         <v>9.6</v>
@@ -3781,13 +3781,13 @@
         <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
         <v>6.8</v>
@@ -3799,7 +3799,7 @@
         <v>19.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY17" t="n">
         <v>16</v>
@@ -3808,29 +3808,29 @@
         <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG17" t="n">
         <v>13</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3861,28 +3861,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="I18" t="n">
-        <v>870</v>
+        <v>9.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
         <v>3.3</v>
@@ -3897,28 +3897,28 @@
         <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
         <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,10 +3939,10 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3951,7 +3951,7 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>1000</v>
@@ -3963,68 +3963,68 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G19" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="H19" t="n">
         <v>5.7</v>
@@ -4067,37 +4067,37 @@
         <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
         <v>1.8</v>
@@ -4106,7 +4106,7 @@
         <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X19" t="n">
         <v>13.5</v>
@@ -4121,7 +4121,7 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="n">
         <v>970</v>
@@ -4145,7 +4145,7 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4181,44 +4181,44 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB19" t="n">
         <v>5</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>4.7</v>
@@ -769,10 +769,10 @@
         <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.51</v>
@@ -787,7 +787,7 @@
         <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
         <v>2.3</v>
@@ -799,128 +799,128 @@
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.87</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.88</v>
       </c>
       <c r="W2" t="n">
         <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>990</v>
       </c>
       <c r="AJ2" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>24</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>2.68</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>2.78</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.2</v>
+        <v>2.86</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>2.82</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>2.82</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>2.86</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -951,124 +951,124 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G3" t="n">
         <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="O3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.65</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.66</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W3" t="n">
         <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="n">
         <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB3" t="n">
         <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF3" t="n">
         <v>32</v>
       </c>
-      <c r="AF3" t="n">
-        <v>34</v>
-      </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AK3" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM3" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
@@ -1080,41 +1080,41 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BA3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BC3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BE3" t="n">
         <v>110</v>
       </c>
       <c r="BF3" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BG3" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
@@ -1169,7 +1169,7 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
@@ -1178,25 +1178,25 @@
         <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X4" t="n">
         <v>13</v>
@@ -1208,7 +1208,7 @@
         <v>20</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB4" t="n">
         <v>10.5</v>
@@ -1217,7 +1217,7 @@
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
         <v>36</v>
@@ -1232,7 +1232,7 @@
         <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
@@ -1247,7 +1247,7 @@
         <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO4" t="n">
         <v>34</v>
@@ -1256,7 +1256,7 @@
         <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>18.5</v>
@@ -1277,7 +1277,7 @@
         <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1298,7 +1298,7 @@
         <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BF4" t="n">
         <v>22</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>4.3</v>
@@ -1357,34 +1357,34 @@
         <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
         <v>1.3</v>
@@ -1393,116 +1393,116 @@
         <v>2</v>
       </c>
       <c r="X5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF5" t="n">
         <v>21</v>
       </c>
-      <c r="Y5" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK5" t="n">
         <v>46</v>
       </c>
-      <c r="AF5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>19</v>
-      </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
         <v>44</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="BE5" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H6" t="n">
         <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
         <v>3.55</v>
@@ -1560,7 +1560,7 @@
         <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
         <v>2.2</v>
@@ -1572,13 +1572,13 @@
         <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
         <v>1.53</v>
@@ -1617,7 +1617,7 @@
         <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI6" t="n">
         <v>95</v>
@@ -1626,7 +1626,7 @@
         <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>85</v>
@@ -1638,25 +1638,25 @@
         <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AT6" t="n">
         <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>11.5</v>
@@ -1665,38 +1665,38 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BF6" t="n">
         <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K7" t="n">
         <v>5.4</v>
@@ -1754,25 +1754,25 @@
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
         <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1781,46 +1781,46 @@
         <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Z7" t="n">
         <v>540</v>
       </c>
       <c r="AA7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>470</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AL7" t="n">
         <v>100</v>
@@ -1829,68 +1829,68 @@
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.5</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>1.81</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G8" t="n">
         <v>2.06</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>1.37</v>
@@ -1945,146 +1945,146 @@
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="Y8" t="n">
         <v>32</v>
       </c>
       <c r="Z8" t="n">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL8" t="n">
         <v>30</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>250</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>75</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>44</v>
       </c>
       <c r="AP8" t="n">
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AR8" t="n">
         <v>14.5</v>
       </c>
       <c r="AS8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT8" t="n">
         <v>10</v>
       </c>
-      <c r="AT8" t="n">
-        <v>9</v>
-      </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
       </c>
       <c r="BC8" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD8" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD8" t="n">
-        <v>16</v>
-      </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
         <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.69</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.71</v>
-      </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
         <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
         <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="AB9" t="n">
         <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AP9" t="n">
         <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
         <v>42</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BB9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BE9" t="n">
-        <v>15.5</v>
+        <v>85</v>
       </c>
       <c r="BF9" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -2309,79 +2309,79 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="I10" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
         <v>500</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>900</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD10" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2402,7 +2402,7 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2420,59 +2420,59 @@
         <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AR10" t="n">
         <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
         <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BB10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG10" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="G11" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>1.54</v>
@@ -2527,61 +2527,61 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O11" t="n">
         <v>1.48</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AC11" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="n">
         <v>36</v>
@@ -2617,56 +2617,56 @@
         <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="AX11" t="n">
         <v>5.8</v>
       </c>
       <c r="AY11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="BD11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>4.9</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
         <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
         <v>4.5</v>
@@ -2724,13 +2724,13 @@
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P12" t="n">
         <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -2745,7 +2745,7 @@
         <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
         <v>1.87</v>
@@ -2790,7 +2790,7 @@
         <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
@@ -2823,10 +2823,10 @@
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX12" t="n">
         <v>10.5</v>
@@ -2835,7 +2835,7 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>12.5</v>
@@ -2847,7 +2847,7 @@
         <v>23</v>
       </c>
       <c r="BD12" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
         <v>13.5</v>
@@ -2856,11 +2856,11 @@
         <v>18.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.57</v>
@@ -2915,49 +2915,49 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
         <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
         <v>8.199999999999999</v>
@@ -2966,52 +2966,52 @@
         <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG13" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ13" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
       <c r="AK13" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
         <v>85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>95</v>
       </c>
       <c r="AO13" t="n">
         <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR13" t="n">
         <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
@@ -3020,41 +3020,41 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5.4</v>
       </c>
-      <c r="BC13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3115,10 +3115,10 @@
         <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R14" t="n">
         <v>1.23</v>
@@ -3127,7 +3127,7 @@
         <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
         <v>1.67</v>
@@ -3136,7 +3136,7 @@
         <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X14" t="n">
         <v>11</v>
@@ -3184,10 +3184,10 @@
         <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO14" t="n">
         <v>260</v>
@@ -3199,19 +3199,19 @@
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AS14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
         <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW14" t="n">
         <v>12.5</v>
@@ -3223,10 +3223,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB14" t="n">
         <v>14.5</v>
@@ -3235,7 +3235,7 @@
         <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BE14" t="n">
         <v>13</v>
@@ -3244,11 +3244,11 @@
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
         <v>4.4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G16" t="n">
         <v>2.8</v>
@@ -3488,7 +3488,7 @@
         <v>2.9</v>
       </c>
       <c r="K16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.56</v>
@@ -3503,7 +3503,7 @@
         <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q16" t="n">
         <v>2.6</v>
@@ -3512,7 +3512,7 @@
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
         <v>2.02</v>
@@ -3545,7 +3545,7 @@
         <v>42</v>
       </c>
       <c r="AD16" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
@@ -3587,10 +3587,10 @@
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -3602,10 +3602,10 @@
         <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.44</v>
+        <v>3.85</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -3614,7 +3614,7 @@
         <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.48</v>
+        <v>1.99</v>
       </c>
       <c r="BB16" t="n">
         <v>1.96</v>
@@ -3623,7 +3623,7 @@
         <v>1.94</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.46</v>
+        <v>1.99</v>
       </c>
       <c r="BE16" t="n">
         <v>2.02</v>
@@ -3632,11 +3632,11 @@
         <v>1.97</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>4.9</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
         <v>1.88</v>
@@ -3679,10 +3679,10 @@
         <v>1.92</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.49</v>
@@ -3709,16 +3709,16 @@
         <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X17" t="n">
         <v>11.5</v>
@@ -3748,13 +3748,13 @@
         <v>48</v>
       </c>
       <c r="AG17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH17" t="n">
         <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -3781,7 +3781,7 @@
         <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS17" t="n">
         <v>18</v>
@@ -3799,10 +3799,10 @@
         <v>19.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>18</v>
@@ -3811,26 +3811,26 @@
         <v>5.8</v>
       </c>
       <c r="BB17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC17" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC17" t="n">
-        <v>6</v>
-      </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H18" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
@@ -3894,31 +3894,31 @@
         <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
         <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X18" t="n">
         <v>15.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3969,19 +3969,19 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ18" t="n">
         <v>3.75</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
         <v>4.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU18" t="n">
         <v>3.15</v>
@@ -3999,19 +3999,19 @@
         <v>3.25</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BA18" t="n">
         <v>4.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BC18" t="n">
         <v>3.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE18" t="n">
         <v>4.3</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H19" t="n">
         <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -4073,40 +4073,40 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V19" t="n">
         <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X19" t="n">
         <v>13.5</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4181,44 +4181,44 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BA19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD19" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6</v>
-      </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="n">
         <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>3.6</v>
@@ -778,16 +778,16 @@
         <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
         <v>2.3</v>
@@ -799,128 +799,128 @@
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="n">
-        <v>980</v>
+        <v>13</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
         <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AG2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>990</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.78</v>
+        <v>40</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.86</v>
+        <v>36</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.82</v>
+        <v>50</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.82</v>
+        <v>60</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.86</v>
+        <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>46</v>
       </c>
       <c r="BG2" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -951,73 +951,73 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
         <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="U3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V3" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="X3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
         <v>7.4</v>
@@ -1026,55 +1026,55 @@
         <v>12</v>
       </c>
       <c r="AE3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="n">
         <v>34</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32</v>
       </c>
       <c r="AI3" t="n">
         <v>80</v>
       </c>
       <c r="AJ3" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AK3" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AL3" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AM3" t="n">
-        <v>320</v>
+        <v>390</v>
       </c>
       <c r="AN3" t="n">
-        <v>170</v>
+        <v>220</v>
       </c>
       <c r="AO3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>11</v>
@@ -1083,25 +1083,25 @@
         <v>29</v>
       </c>
       <c r="AX3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AY3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA3" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BB3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BC3" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BD3" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BE3" t="n">
         <v>110</v>
@@ -1110,11 +1110,11 @@
         <v>65</v>
       </c>
       <c r="BG3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1157,7 +1157,7 @@
         <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>3.5</v>
@@ -1175,46 +1175,46 @@
         <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
         <v>1.61</v>
       </c>
       <c r="X4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4" t="n">
         <v>11.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
         <v>13.5</v>
@@ -1232,7 +1232,7 @@
         <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
@@ -1247,10 +1247,10 @@
         <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
@@ -1262,19 +1262,19 @@
         <v>18.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX4" t="n">
         <v>15</v>
@@ -1286,29 +1286,29 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
         <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF4" t="n">
         <v>23</v>
       </c>
-      <c r="BE4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>22</v>
-      </c>
       <c r="BG4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>1.99</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.42</v>
@@ -1363,106 +1363,106 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
         <v>2.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
         <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
         <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="AP5" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
         <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
@@ -1477,22 +1477,22 @@
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BF5" t="n">
         <v>11.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="n">
         <v>2.72</v>
@@ -1545,55 +1545,55 @@
         <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.52</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.53</v>
       </c>
       <c r="W6" t="n">
         <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y6" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
         <v>85</v>
@@ -1608,76 +1608,76 @@
         <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AF6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
         <v>15.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
         <v>85</v>
       </c>
       <c r="AM6" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AO6" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
         <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
         <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="BC6" t="n">
         <v>13</v>
@@ -1686,17 +1686,17 @@
         <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G7" t="n">
         <v>1.41</v>
@@ -1736,7 +1736,7 @@
         <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J7" t="n">
         <v>4.9</v>
@@ -1751,28 +1751,28 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
         <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1781,46 +1781,46 @@
         <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="Z7" t="n">
         <v>540</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>48</v>
       </c>
       <c r="AI7" t="n">
         <v>470</v>
       </c>
       <c r="AJ7" t="n">
-        <v>900</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
         <v>100</v>
@@ -1829,68 +1829,68 @@
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>29</v>
+        <v>7.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AP7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AS7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV7" t="n">
         <v>16.5</v>
       </c>
-      <c r="AR7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="AW7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF7" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G8" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -1951,49 +1951,49 @@
         <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
         <v>2.94</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
         <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z8" t="n">
         <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
         <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>48</v>
@@ -2002,28 +2002,28 @@
         <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ8" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
         <v>19.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AO8" t="n">
         <v>44</v>
@@ -2035,10 +2035,10 @@
         <v>16.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2047,13 +2047,13 @@
         <v>7.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>9.4</v>
@@ -2062,29 +2062,29 @@
         <v>14.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
         <v>17</v>
       </c>
       <c r="BD8" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="G9" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>1.43</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
         <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA9" t="n">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="AB9" t="n">
         <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
         <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AK9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>540</v>
+        <v>150</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS9" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC9" t="n">
         <v>15.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2318,10 +2318,10 @@
         <v>2.12</v>
       </c>
       <c r="I10" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
         <v>3.4</v>
@@ -2342,22 +2342,22 @@
         <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2372,10 +2372,10 @@
         <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
         <v>14</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.54</v>
@@ -2527,40 +2527,40 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="O11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="X11" t="n">
         <v>17</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,23 +2569,23 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG11" t="n">
         <v>30</v>
       </c>
-      <c r="AG11" t="n">
-        <v>36</v>
-      </c>
       <c r="AH11" t="n">
         <v>1000</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
         <v>110</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>9</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
         <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
         <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
         <v>3.4</v>
@@ -2721,31 +2721,31 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
         <v>1.87</v>
@@ -2754,22 +2754,22 @@
         <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
         <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC12" t="n">
         <v>7.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE12" t="n">
         <v>70</v>
@@ -2799,7 +2799,7 @@
         <v>160</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>95</v>
@@ -2808,13 +2808,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
@@ -2823,10 +2823,10 @@
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
         <v>10.5</v>
@@ -2838,29 +2838,29 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BB12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC12" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="BD12" t="n">
         <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BF12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG12" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.57</v>
@@ -2915,64 +2915,64 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O13" t="n">
         <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
         <v>9.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH13" t="n">
         <v>24</v>
@@ -2987,31 +2987,31 @@
         <v>160</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
         <v>11.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
@@ -3020,41 +3020,41 @@
         <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.3</v>
+        <v>17.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3085,82 +3085,82 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G14" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="H14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
         <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
         <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="X14" t="n">
         <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
         <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AB14" t="n">
         <v>6.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF14" t="n">
         <v>8.6</v>
@@ -3169,86 +3169,86 @@
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>160</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>700</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="AP14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS14" t="n">
         <v>15</v>
       </c>
-      <c r="AR14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>13</v>
-      </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW14" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD14" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF14" t="n">
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
         <v>4.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
         <v>3.15</v>
@@ -3336,16 +3336,16 @@
         <v>9.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
         <v>970</v>
@@ -3369,7 +3369,7 @@
         <v>170</v>
       </c>
       <c r="AJ15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK15" t="n">
         <v>40</v>
@@ -3381,7 +3381,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
@@ -3396,7 +3396,7 @@
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AT15" t="n">
         <v>6.2</v>
@@ -3408,7 +3408,7 @@
         <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -3420,29 +3420,29 @@
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>21</v>
+        <v>3.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BE15" t="n">
         <v>140</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BG15" t="n">
         <v>3.55</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="H16" t="n">
         <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
         <v>3.1</v>
@@ -3503,7 +3503,7 @@
         <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
         <v>2.6</v>
@@ -3512,7 +3512,7 @@
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T16" t="n">
         <v>2.02</v>
@@ -3530,7 +3530,7 @@
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,28 +3539,28 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AC16" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
         <v>170</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
         <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AH16" t="n">
         <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
         <v>900</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.99</v>
+        <v>3.85</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA16" t="n">
         <v>3.85</v>
       </c>
-      <c r="AX16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.99</v>
-      </c>
       <c r="BB16" t="n">
-        <v>1.96</v>
+        <v>10.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.94</v>
+        <v>10</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.99</v>
+        <v>3.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.97</v>
+        <v>3.7</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="I17" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3697,61 +3697,61 @@
         <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
         <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AB17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD17" t="n">
         <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3772,65 +3772,65 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY17" t="n">
         <v>19.5</v>
       </c>
-      <c r="AX17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.45</v>
@@ -3903,10 +3903,10 @@
         <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
@@ -3939,7 +3939,7 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>12.5</v>
@@ -3954,7 +3954,7 @@
         <v>19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AR18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS18" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS18" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AT18" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
         <v>3.1</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>1.78</v>
       </c>
       <c r="H19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
@@ -4082,34 +4082,34 @@
         <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
         <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V19" t="n">
         <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X19" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
         <v>1000</v>
@@ -4121,10 +4121,10 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
         <v>950</v>
@@ -4133,10 +4133,10 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
         <v>950</v>
@@ -4145,13 +4145,13 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4181,44 +4181,44 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AW19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD19" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF19" t="n">
         <v>10.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -766,64 +766,64 @@
         <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
         <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
         <v>8</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC2" t="n">
         <v>7.8</v>
@@ -832,58 +832,58 @@
         <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>370</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN2" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
         <v>6.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
         <v>21</v>
@@ -892,35 +892,35 @@
         <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
         <v>36</v>
       </c>
       <c r="BC2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BD2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BE2" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BG2" t="n">
         <v>17.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>5.2</v>
@@ -963,37 +963,37 @@
         <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="U3" t="n">
         <v>1.61</v>
@@ -1002,22 +1002,22 @@
         <v>1.96</v>
       </c>
       <c r="W3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
         <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
         <v>7.4</v>
@@ -1032,13 +1032,13 @@
         <v>36</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH3" t="n">
         <v>34</v>
       </c>
       <c r="AI3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ3" t="n">
         <v>160</v>
@@ -1047,13 +1047,13 @@
         <v>120</v>
       </c>
       <c r="AL3" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AM3" t="n">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="AN3" t="n">
-        <v>220</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
         <v>32</v>
@@ -1065,34 +1065,34 @@
         <v>5.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
         <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AX3" t="n">
         <v>32</v>
       </c>
       <c r="AY3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB3" t="n">
         <v>80</v>
@@ -1110,11 +1110,11 @@
         <v>65</v>
       </c>
       <c r="BG3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
@@ -1184,7 +1184,7 @@
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T4" t="n">
         <v>1.83</v>
@@ -1193,16 +1193,16 @@
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X4" t="n">
         <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z4" t="n">
         <v>21</v>
@@ -1211,37 +1211,37 @@
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>36</v>
       </c>
       <c r="AF4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
         <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>100</v>
@@ -1250,7 +1250,7 @@
         <v>25</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
@@ -1262,10 +1262,10 @@
         <v>18.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
@@ -1274,7 +1274,7 @@
         <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
         <v>15</v>
@@ -1286,29 +1286,29 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
         <v>32</v>
       </c>
       <c r="BC4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
         <v>60</v>
       </c>
       <c r="BF4" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="BG4" t="n">
         <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.97</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.99</v>
-      </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
@@ -1357,70 +1357,70 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
         <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
@@ -1429,31 +1429,31 @@
         <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS5" t="n">
         <v>65</v>
@@ -1465,10 +1465,10 @@
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1480,7 +1480,7 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1492,17 +1492,17 @@
         <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
         <v>34</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1533,28 +1533,28 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H6" t="n">
         <v>2.74</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.72</v>
-      </c>
       <c r="I6" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.38</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
         <v>4.5</v>
@@ -1563,140 +1563,140 @@
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X6" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AB6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AF6" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>15.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AJ6" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>70</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
         <v>12</v>
       </c>
-      <c r="AR6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AW6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF6" t="n">
         <v>18</v>
       </c>
-      <c r="BB6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BG6" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1733,19 +1733,19 @@
         <v>1.41</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
@@ -1754,7 +1754,7 @@
         <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
         <v>2.06</v>
@@ -1763,16 +1763,16 @@
         <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
         <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1781,116 +1781,116 @@
         <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>540</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>520</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
         <v>470</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="AO7" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AV7" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
         <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>2.12</v>
       </c>
       <c r="BE7" t="n">
-        <v>13.5</v>
+        <v>3.55</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1936,31 +1936,31 @@
         <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="T8" t="n">
         <v>1.67</v>
@@ -1969,16 +1969,16 @@
         <v>2.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="Z8" t="n">
         <v>34</v>
@@ -1990,88 +1990,88 @@
         <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
         <v>13.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="n">
         <v>19.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN8" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX8" t="n">
         <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE8" t="n">
         <v>13.5</v>
@@ -2080,11 +2080,11 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2115,67 +2115,67 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
         <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
         <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
         <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA9" t="n">
         <v>210</v>
@@ -2184,49 +2184,49 @@
         <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
         <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AG9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL9" t="n">
         <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR9" t="n">
         <v>46</v>
@@ -2235,31 +2235,31 @@
         <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AX9" t="n">
         <v>8.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BB9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC9" t="n">
         <v>15.5</v>
@@ -2268,7 +2268,7 @@
         <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="BF9" t="n">
         <v>8.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G10" t="n">
         <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I10" t="n">
         <v>2.24</v>
@@ -2324,34 +2324,34 @@
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
         <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
         <v>1.78</v>
@@ -2360,13 +2360,13 @@
         <v>1.8</v>
       </c>
       <c r="W10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2375,13 +2375,13 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2402,7 +2402,7 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2417,13 +2417,13 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AS10" t="n">
         <v>9</v>
@@ -2435,44 +2435,44 @@
         <v>4.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>3.15</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>3.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.6</v>
+        <v>2.02</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>1.94</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.6</v>
+        <v>1.94</v>
       </c>
       <c r="BD10" t="n">
-        <v>36</v>
+        <v>1.94</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>2.04</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>1.94</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
@@ -2521,152 +2521,152 @@
         <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>1.49</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
         <v>4.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="n">
         <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF11" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>6</v>
-      </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2706,13 +2706,13 @@
         <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>1.52</v>
@@ -2721,16 +2721,16 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -2739,7 +2739,7 @@
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
         <v>1.86</v>
@@ -2748,7 +2748,7 @@
         <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -2763,13 +2763,13 @@
         <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="AC12" t="n">
         <v>7.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>70</v>
@@ -2784,13 +2784,13 @@
         <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ12" t="n">
         <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
@@ -2805,31 +2805,31 @@
         <v>95</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AT12" t="n">
         <v>6.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
         <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
@@ -2838,29 +2838,29 @@
         <v>20</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BB12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD12" t="n">
         <v>23</v>
       </c>
-      <c r="BC12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>24</v>
-      </c>
       <c r="BE12" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="n">
         <v>4.1</v>
@@ -2906,10 +2906,10 @@
         <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
@@ -2921,7 +2921,7 @@
         <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
         <v>2.62</v>
@@ -2933,10 +2933,10 @@
         <v>5.3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>1.71</v>
@@ -2945,25 +2945,25 @@
         <v>1.33</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y13" t="n">
         <v>7.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB13" t="n">
         <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE13" t="n">
         <v>34</v>
@@ -2972,7 +2972,7 @@
         <v>28</v>
       </c>
       <c r="AG13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
         <v>24</v>
@@ -2984,7 +2984,7 @@
         <v>260</v>
       </c>
       <c r="AK13" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="AL13" t="n">
         <v>500</v>
@@ -2996,65 +2996,65 @@
         <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
         <v>1.74</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
         <v>6.8</v>
@@ -3100,7 +3100,7 @@
         <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.54</v>
@@ -3127,10 +3127,10 @@
         <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U14" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
@@ -3139,13 +3139,13 @@
         <v>2.34</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
         <v>230</v>
@@ -3157,7 +3157,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
         <v>130</v>
@@ -3169,19 +3169,19 @@
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>160</v>
       </c>
       <c r="AJ14" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
         <v>700</v>
@@ -3193,62 +3193,62 @@
         <v>220</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>7.4</v>
       </c>
       <c r="AT14" t="n">
         <v>5.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF14" t="n">
         <v>14</v>
       </c>
-      <c r="BB14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>13</v>
-      </c>
       <c r="BG14" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
         <v>3.1</v>
@@ -3500,10 +3500,10 @@
         <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q16" t="n">
         <v>2.6</v>
@@ -3512,25 +3512,25 @@
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="Y16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,22 +3539,22 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD16" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
         <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.4</v>
+        <v>1.54</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.85</v>
+        <v>1.43</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.6</v>
+        <v>3.95</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="AW16" t="n">
-        <v>11</v>
+        <v>1.54</v>
       </c>
       <c r="AX16" t="n">
-        <v>7.4</v>
+        <v>1.78</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8.4</v>
+        <v>2.36</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.85</v>
+        <v>1.44</v>
       </c>
       <c r="BB16" t="n">
-        <v>10.5</v>
+        <v>1.54</v>
       </c>
       <c r="BC16" t="n">
-        <v>10</v>
+        <v>1.54</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>1.43</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.56</v>
+        <v>1.44</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.7</v>
+        <v>1.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G17" t="n">
         <v>5.4</v>
       </c>
-      <c r="G17" t="n">
-        <v>6</v>
-      </c>
       <c r="H17" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="I17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.5</v>
@@ -3694,19 +3694,19 @@
         <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T17" t="n">
         <v>1.98</v>
@@ -3715,43 +3715,43 @@
         <v>1.84</v>
       </c>
       <c r="V17" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3772,65 +3772,65 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.800000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.2</v>
+        <v>1.97</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.6</v>
+        <v>2.1</v>
       </c>
       <c r="AS17" t="n">
         <v>16</v>
       </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>2.14</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.800000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AY17" t="n">
-        <v>19.5</v>
+        <v>2.18</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19.5</v>
+        <v>2.26</v>
       </c>
       <c r="BA17" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>2.42</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.6</v>
+        <v>2.42</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>2.42</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>2.42</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.8</v>
+        <v>2.42</v>
       </c>
       <c r="BG17" t="n">
         <v>11</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G18" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="H18" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I18" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K18" t="n">
         <v>4.2</v>
@@ -3882,7 +3882,7 @@
         <v>1.45</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
         <v>3.3</v>
@@ -3891,7 +3891,7 @@
         <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
         <v>2.12</v>
@@ -3903,22 +3903,22 @@
         <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,10 +3927,10 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
         <v>1000</v>
@@ -3939,10 +3939,10 @@
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3951,10 +3951,10 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
@@ -3963,68 +3963,68 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G19" t="n">
         <v>1.74</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.78</v>
       </c>
       <c r="H19" t="n">
         <v>5.8</v>
@@ -4067,10 +4067,10 @@
         <v>6.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>1.44</v>
@@ -4079,37 +4079,37 @@
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
         <v>1000</v>
@@ -4121,37 +4121,37 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5</v>
+        <v>130</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>950</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>1.38</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>1.58</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.92</v>
+        <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>1.69</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>19.5</v>
+        <v>2.74</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>2.74</v>
       </c>
       <c r="BB2" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
-        <v>40</v>
+        <v>2.74</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>1.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>17.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -954,58 +954,58 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="M3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W3" t="n">
         <v>1.23</v>
       </c>
       <c r="X3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y3" t="n">
         <v>5.8</v>
@@ -1014,31 +1014,31 @@
         <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB3" t="n">
         <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
         <v>12</v>
       </c>
       <c r="AE3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH3" t="n">
         <v>32</v>
       </c>
-      <c r="AF3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>34</v>
-      </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
         <v>160</v>
@@ -1047,19 +1047,19 @@
         <v>120</v>
       </c>
       <c r="AL3" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AN3" t="n">
-        <v>600</v>
+        <v>220</v>
       </c>
       <c r="AO3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.4</v>
@@ -1071,10 +1071,10 @@
         <v>22</v>
       </c>
       <c r="AT3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
         <v>11</v>
@@ -1086,22 +1086,22 @@
         <v>32</v>
       </c>
       <c r="AY3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA3" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BC3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BD3" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BE3" t="n">
         <v>110</v>
@@ -1110,11 +1110,11 @@
         <v>65</v>
       </c>
       <c r="BG3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -1169,76 +1169,76 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="X4" t="n">
         <v>13.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
         <v>42</v>
@@ -1247,68 +1247,68 @@
         <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC4" t="n">
         <v>24</v>
       </c>
-      <c r="AX4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BD4" t="n">
         <v>36</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>30</v>
       </c>
       <c r="BE4" t="n">
         <v>60</v>
       </c>
       <c r="BF4" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BG4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.96</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.97</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -1351,10 +1351,10 @@
         <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.41</v>
@@ -1369,10 +1369,10 @@
         <v>1.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
@@ -1390,19 +1390,19 @@
         <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
         <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="n">
         <v>9.4</v>
@@ -1411,7 +1411,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
         <v>55</v>
@@ -1432,31 +1432,31 @@
         <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL5" t="n">
         <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
@@ -1498,11 +1498,11 @@
         <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1536,79 +1536,79 @@
         <v>2.72</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I6" t="n">
         <v>2.74</v>
       </c>
-      <c r="I6" t="n">
-        <v>2.8</v>
-      </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.56</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.54</v>
-      </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
         <v>14</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
         <v>21</v>
@@ -1617,10 +1617,10 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
         <v>42</v>
@@ -1632,16 +1632,16 @@
         <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>18.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>13</v>
@@ -1653,19 +1653,19 @@
         <v>34</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
         <v>12</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
         <v>12</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB6" t="n">
         <v>36</v>
       </c>
       <c r="BC6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
         <v>1.41</v>
       </c>
       <c r="H7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.4</v>
@@ -1769,10 +1769,10 @@
         <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1781,116 +1781,116 @@
         <v>3.4</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI7" t="n">
         <v>470</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
         <v>390</v>
       </c>
       <c r="AN7" t="n">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.2</v>
+        <v>65</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.12</v>
+        <v>27</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.55</v>
+        <v>36</v>
       </c>
       <c r="BF7" t="n">
         <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G8" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
         <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -1948,37 +1948,37 @@
         <v>4.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T8" t="n">
         <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
         <v>34</v>
@@ -1990,13 +1990,13 @@
         <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="n">
         <v>13.5</v>
@@ -2005,52 +2005,52 @@
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AI8" t="n">
         <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL8" t="n">
         <v>30</v>
       </c>
       <c r="AM8" t="n">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AO8" t="n">
         <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AS8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT8" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10</v>
       </c>
       <c r="AU8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AX8" t="n">
         <v>12</v>
@@ -2062,29 +2062,29 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BB8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
         <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BE8" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BF8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.59</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="H9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J9" t="n">
         <v>4.4</v>
@@ -2145,40 +2145,40 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
         <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
         <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
         <v>21</v>
       </c>
       <c r="Z9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA9" t="n">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AB9" t="n">
         <v>8</v>
@@ -2190,16 +2190,16 @@
         <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>100</v>
@@ -2220,19 +2220,19 @@
         <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="AP9" t="n">
         <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AT9" t="n">
         <v>7.6</v>
@@ -2241,10 +2241,10 @@
         <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AX9" t="n">
         <v>8.6</v>
@@ -2253,10 +2253,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BB9" t="n">
         <v>14</v>
@@ -2265,20 +2265,20 @@
         <v>15.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE9" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG9" t="n">
         <v>100</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G10" t="n">
         <v>4.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I10" t="n">
         <v>2.24</v>
@@ -2324,19 +2324,19 @@
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L10" t="n">
         <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
         <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P10" t="n">
         <v>1.6</v>
@@ -2348,25 +2348,25 @@
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W10" t="n">
         <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z10" t="n">
         <v>1000</v>
@@ -2375,13 +2375,13 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2390,7 +2390,7 @@
         <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2402,10 +2402,10 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,13 +2417,13 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS10" t="n">
         <v>9</v>
@@ -2432,47 +2432,47 @@
         <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.15</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.1</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.02</v>
+        <v>8.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.94</v>
+        <v>10</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.94</v>
+        <v>5.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.94</v>
+        <v>32</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.04</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.94</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
         <v>2.38</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -2539,16 +2539,16 @@
         <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
         <v>4.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
         <v>1.34</v>
@@ -2557,7 +2557,7 @@
         <v>1.72</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="Y11" t="n">
         <v>11.5</v>
@@ -2566,10 +2566,10 @@
         <v>95</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
         <v>7.4</v>
@@ -2593,7 +2593,7 @@
         <v>85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="n">
         <v>32</v>
@@ -2611,7 +2611,7 @@
         <v>80</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.4</v>
@@ -2623,50 +2623,50 @@
         <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
         <v>11.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BB11" t="n">
         <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
         <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.52</v>
@@ -2727,10 +2727,10 @@
         <v>1.47</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -2739,16 +2739,16 @@
         <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.86</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.89</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
@@ -2760,16 +2760,16 @@
         <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="n">
-        <v>14.5</v>
+        <v>7.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
         <v>70</v>
@@ -2784,7 +2784,7 @@
         <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="n">
         <v>26</v>
@@ -2802,65 +2802,65 @@
         <v>23</v>
       </c>
       <c r="AO12" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AS12" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
         <v>16.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF12" t="n">
         <v>20</v>
       </c>
-      <c r="BA12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>11</v>
-      </c>
       <c r="BG12" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G13" t="n">
         <v>4.1</v>
@@ -2909,16 +2909,16 @@
         <v>3.3</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
         <v>1.56</v>
@@ -2936,7 +2936,7 @@
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V13" t="n">
         <v>1.71</v>
@@ -2945,16 +2945,16 @@
         <v>1.33</v>
       </c>
       <c r="X13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13" t="n">
         <v>7.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB13" t="n">
         <v>11.5</v>
@@ -2966,7 +2966,7 @@
         <v>12.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
         <v>28</v>
@@ -2978,83 +2978,83 @@
         <v>24</v>
       </c>
       <c r="AI13" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="AK13" t="n">
         <v>70</v>
       </c>
       <c r="AL13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO13" t="n">
         <v>500</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>34</v>
       </c>
       <c r="AP13" t="n">
         <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR13" t="n">
         <v>11</v>
       </c>
       <c r="AS13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY13" t="n">
         <v>15</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>14.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>19.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3094,13 +3094,13 @@
         <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
         <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
         <v>1.54</v>
@@ -3112,10 +3112,10 @@
         <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
         <v>2.46</v>
@@ -3130,7 +3130,7 @@
         <v>2.32</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
         <v>1.17</v>
@@ -3139,13 +3139,13 @@
         <v>2.34</v>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y14" t="n">
         <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
         <v>230</v>
@@ -3157,7 +3157,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
         <v>130</v>
@@ -3169,40 +3169,40 @@
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AI14" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AJ14" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
         <v>700</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO14" t="n">
         <v>220</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="AT14" t="n">
         <v>5.8</v>
@@ -3214,41 +3214,41 @@
         <v>23</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BB14" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BD14" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BF14" t="n">
         <v>14</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="G15" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P15" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.02</v>
+        <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
         <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO15" t="n">
         <v>95</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
       </c>
       <c r="AP15" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.55</v>
+        <v>42</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.6</v>
+        <v>55</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.5</v>
+        <v>22</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.55</v>
+        <v>42</v>
       </c>
       <c r="BE15" t="n">
         <v>140</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.35</v>
+        <v>15</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="K16" t="n">
         <v>3.1</v>
@@ -3500,10 +3500,10 @@
         <v>2.76</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q16" t="n">
         <v>2.6</v>
@@ -3512,64 +3512,64 @@
         <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
         <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z16" t="n">
         <v>500</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA16" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AH16" t="n">
         <v>42</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>210</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.54</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.43</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.58</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.54</v>
+        <v>10.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.78</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.44</v>
+        <v>11</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.54</v>
+        <v>10</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.43</v>
+        <v>11</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.44</v>
+        <v>7</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.55</v>
+        <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.55</v>
+        <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.5</v>
@@ -3691,13 +3691,13 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
         <v>2.28</v>
@@ -3709,40 +3709,40 @@
         <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
         <v>2.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AF17" t="n">
         <v>1000</v>
@@ -3751,7 +3751,7 @@
         <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3772,72 +3772,72 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.42</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.97</v>
+        <v>6.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.14</v>
+        <v>12.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.08</v>
+        <v>9</v>
       </c>
       <c r="AW17" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>25</v>
+        <v>6.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.18</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.26</v>
+        <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>29</v>
+        <v>6.8</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.42</v>
+        <v>7.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.42</v>
+        <v>7</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.42</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.42</v>
+        <v>7.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.42</v>
+        <v>7.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>3.75</v>
       </c>
       <c r="G18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.72</v>
       </c>
-      <c r="H18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="W18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="AW18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>4.2</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,184 +4041,378 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aguilas Doradas</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="G19" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I19" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:43:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W20" t="n">
         <v>2.32</v>
       </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-31 10:36:15</t>
+      <c r="X20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH20"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>95</v>
+      </c>
+      <c r="G2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.03</v>
       </c>
-      <c r="G2" t="n">
-        <v>130</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.8</v>
-      </c>
       <c r="I2" t="n">
-        <v>950</v>
+        <v>1.04</v>
       </c>
       <c r="J2" t="n">
-        <v>1.38</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
-        <v>1.58</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,28 +787,28 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14</v>
+        <v>26</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -817,10 +817,10 @@
         <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
         <v>1000</v>
@@ -829,10 +829,10 @@
         <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
@@ -841,10 +841,10 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -853,81 +853,81 @@
         <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.69</v>
+        <v>440</v>
       </c>
       <c r="AN2" t="n">
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.74</v>
+        <v>26</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.74</v>
+        <v>14.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.74</v>
+        <v>180</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.55</v>
+        <v>180</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -942,179 +942,179 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>1.37</v>
       </c>
       <c r="G3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>420</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX3" t="n">
         <v>5.3</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AY3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="n">
         <v>12</v>
       </c>
-      <c r="AC3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="BC3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>180</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>160</v>
       </c>
-      <c r="AK3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>220</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>25</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="G4" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="X4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AA4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI4" t="n">
         <v>60</v>
       </c>
-      <c r="AB4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AJ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU4" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AV4" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AW4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA4" t="n">
         <v>50</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="BB4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC4" t="n">
         <v>20</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>50</v>
       </c>
-      <c r="AT4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>34</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.94</v>
+        <v>2.72</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>2.84</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>280</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AI5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>60</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>22</v>
-      </c>
       <c r="AK5" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>17.5</v>
       </c>
       <c r="AP5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG5" t="n">
         <v>15.5</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>50</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78</v>
+        <v>1.41</v>
       </c>
       <c r="H6" t="n">
-        <v>2.68</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2.74</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>1.78</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>490</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>470</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>270</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC6" t="n">
         <v>14</v>
       </c>
-      <c r="Z6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="BD6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG6" t="n">
         <v>15</v>
       </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>17</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="G7" t="n">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="H7" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W7" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.4</v>
-      </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>530</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>70</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="n">
-        <v>470</v>
+        <v>250</v>
       </c>
       <c r="AJ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX7" t="n">
         <v>12</v>
       </c>
-      <c r="AK7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>330</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="BA7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD7" t="n">
         <v>25</v>
       </c>
-      <c r="AW7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>27</v>
-      </c>
       <c r="BE7" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.5</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="W8" t="n">
-        <v>2.04</v>
+        <v>2.72</v>
       </c>
       <c r="X8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE8" t="n">
         <v>90</v>
       </c>
-      <c r="AB8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>28</v>
-      </c>
       <c r="BF8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,184 +2101,184 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Real Santander</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.59</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>2.12</v>
       </c>
       <c r="I9" t="n">
-        <v>7.2</v>
+        <v>2.24</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="W9" t="n">
-        <v>2.68</v>
+        <v>1.27</v>
       </c>
       <c r="X9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>16</v>
       </c>
-      <c r="Y9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>21</v>
-      </c>
       <c r="BA9" t="n">
-        <v>80</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BE9" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.6</v>
+        <v>3.35</v>
       </c>
       <c r="BG9" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -2300,55 +2300,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.1</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I10" t="n">
         <v>4.7</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.24</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
         <v>2.08</v>
@@ -2357,129 +2357,129 @@
         <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>9.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>7.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK10" t="n">
-        <v>700</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU10" t="n">
         <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.4</v>
+        <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA11" t="n">
         <v>95</v>
       </c>
-      <c r="AA11" t="n">
-        <v>85</v>
-      </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC11" t="n">
         <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
         <v>85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="AK11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AS11" t="n">
         <v>28</v>
       </c>
       <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU11" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AX11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="BE11" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Club 2 de Mayo de Pedro Juan Cab</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>2.28</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.52</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.47</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>1.86</v>
+        <v>1.33</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>34</v>
-      </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BB12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BE12" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Juan Cab</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Cuiaba</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>1.76</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
-        <v>1.33</v>
+        <v>2.32</v>
       </c>
       <c r="X13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP13" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AQ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU13" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB13" t="n">
         <v>16.5</v>
       </c>
-      <c r="AY13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BC13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="BF13" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cuiaba</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>1.74</v>
+        <v>2.48</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>3.65</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="P14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.34</v>
-      </c>
       <c r="X14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y14" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Z14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA14" t="n">
         <v>55</v>
       </c>
-      <c r="AA14" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="BB14" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC14" t="n">
         <v>26</v>
       </c>
-      <c r="AE14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI14" t="n">
+      <c r="BD14" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE14" t="n">
         <v>140</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>28</v>
-      </c>
       <c r="BF14" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="BG14" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Boca Juniors de Cali</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>3.1</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M15" t="n">
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="O15" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="X15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AB15" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="AE15" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG15" t="n">
         <v>65</v>
       </c>
-      <c r="AF15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AI15" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>270</v>
       </c>
       <c r="AM15" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>26</v>
-      </c>
       <c r="BD15" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="BE15" t="n">
-        <v>140</v>
+        <v>12.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,117 +3459,117 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>1.94</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>1.99</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="X16" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AH16" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR16" t="n">
         <v>10</v>
       </c>
       <c r="AS16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT16" t="n">
         <v>11</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC16" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BD16" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>11</v>
-      </c>
       <c r="BE16" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="H17" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="I17" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
         <v>1.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="X17" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="AB17" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC17" t="n">
         <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO17" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AP17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT17" t="n">
         <v>10</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AU17" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="AV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD17" t="n">
         <v>5.9</v>
       </c>
-      <c r="AT17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE17" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="BG17" t="n">
-        <v>15.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.75</v>
+        <v>1.62</v>
       </c>
       <c r="G18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.9</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.8</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>2.46</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>85</v>
+        <v>18.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
         <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AU18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW18" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AX18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF18" t="n">
         <v>10</v>
       </c>
-      <c r="AW18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG18" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,378 +4041,184 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
         <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>40</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>10.5</v>
       </c>
       <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT19" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.2</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BC19" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Aguilas Doradas</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="H20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19:45:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Boca Juniors de Cali</t>
+          <t>Aguilas Doradas</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.4</v>
+        <v>1.23</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8</v>
+        <v>690</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>690</v>
       </c>
       <c r="J2" t="n">
-        <v>1.76</v>
+        <v>5.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.85</v>
+        <v>240</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>2.72</v>
       </c>
       <c r="S2" t="n">
-        <v>5.8</v>
+        <v>1.56</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,877 +826,101 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>360</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AP2" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.99</v>
+        <v>25</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BC2" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>80</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="BF2" t="n">
-        <v>140</v>
+        <v>7.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Paraguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sportivo Luqueno</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Cerro Porteno</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>65</v>
-      </c>
-      <c r="G3" t="n">
-        <v>110</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="J3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>75</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2026-03-31 21:14:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Paraguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Sportivo San Lorenzo</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Club Sportivo Ameliano</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>36</v>
-      </c>
-      <c r="G4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>230</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>120</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-03-31 21:14:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Real Cartagena</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="H5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>19</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>620</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>880</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>220</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>990</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>990</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026-03-31 21:14:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Tolima</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Aguilas Doradas</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
